--- a/output/pdf_financials_xlsx/BRO.xlsx
+++ b/output/pdf_financials_xlsx/BRO.xlsx
@@ -4686,31 +4686,31 @@
         <v>1.561278</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>1.561278</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>2.743098</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>1.808927</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>1.975962</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>2.565328</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>2.672111</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>3.204591</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>2.427756</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>3.104331</v>
       </c>
     </row>
     <row r="93">
@@ -5844,31 +5844,31 @@
         <v>0</v>
       </c>
       <c r="E118" s="3" t="n">
-        <v>0</v>
+        <v>-0.100073</v>
       </c>
       <c r="F118" s="3" t="n">
-        <v>2.04</v>
+        <v>0.501489</v>
       </c>
       <c r="G118" s="3" t="n">
-        <v>1.357395</v>
+        <v>-0.486614</v>
       </c>
       <c r="H118" s="3" t="n">
-        <v>0.6358780000000001</v>
+        <v>-0.691203</v>
       </c>
       <c r="I118" s="3" t="n">
-        <v>1.065351</v>
+        <v>-0.3603</v>
       </c>
       <c r="J118" s="3" t="n">
-        <v>0.089479</v>
+        <v>-3.731866</v>
       </c>
       <c r="K118" s="3" t="n">
-        <v>0</v>
+        <v>-2.899232</v>
       </c>
       <c r="L118" s="3" t="n">
-        <v>1.518494</v>
+        <v>-4.648194</v>
       </c>
       <c r="M118" s="3" t="n">
-        <v>1.66653</v>
+        <v>-4.755906</v>
       </c>
     </row>
     <row r="119">
@@ -7640,7 +7640,11 @@
           <t>Reserves (Note 8)</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
           <t>-</t>
@@ -8228,7 +8232,11 @@
           <t>Reserves (Note 9)</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr"/>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E22" t="inlineStr">
         <is>
           <t>-</t>
@@ -8902,7 +8910,11 @@
           <t>Reserves (Note 10)</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr"/>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E31" t="inlineStr">
         <is>
           <t>-</t>
@@ -9048,7 +9060,11 @@
           <t>Prepaids and deposits</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr"/>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>PrepaidAssets</t>
+        </is>
+      </c>
       <c r="E33" t="inlineStr">
         <is>
           <t>-</t>
@@ -9352,7 +9368,11 @@
           <t>Reserves (Note 7)</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr"/>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E37" t="inlineStr">
         <is>
           <t>-</t>
@@ -9736,7 +9756,11 @@
           <t>Reserves (Note 6)</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr"/>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E42" t="inlineStr">
         <is>
           <t>-</t>
@@ -10196,7 +10220,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr"/>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E48" t="inlineStr">
         <is>
           <t>-</t>
@@ -12164,7 +12192,11 @@
           <t>Exploration and evaluation asset expenditures</t>
         </is>
       </c>
-      <c r="D75" t="inlineStr"/>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E75" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/BRO.xlsx
+++ b/output/pdf_financials_xlsx/BRO.xlsx
@@ -912,25 +912,25 @@
         <v>0</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>0.034357</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>0.057159</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>0.01381</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>0.165263</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>0.055764</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>0.087312</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0</v>
+        <v>0.016258</v>
       </c>
     </row>
     <row r="13">
@@ -1633,25 +1633,25 @@
         <v>-1.97038</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-2.772445</v>
+        <v>-2.806802</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-2.000258</v>
+        <v>-2.057417</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-2.234694</v>
+        <v>-2.248504</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>-1.917313</v>
+        <v>-2.082576</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-3.537643</v>
+        <v>-3.593407</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>-4.571344</v>
+        <v>-4.658656</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>-4.005722</v>
+        <v>-4.02198</v>
       </c>
     </row>
     <row r="28">
@@ -1723,25 +1723,25 @@
         <v>-1.97038</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-2.772445</v>
+        <v>-2.806802</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-1.975319</v>
+        <v>-2.032478</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-2.195989</v>
+        <v>-2.209799</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-1.885631</v>
+        <v>-2.050894</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-3.510768</v>
+        <v>-3.566532</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-4.544469</v>
+        <v>-4.631781</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-3.978847</v>
+        <v>-3.995105</v>
       </c>
     </row>
     <row r="30">
@@ -1942,37 +1942,37 @@
         </is>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>3.8e-05</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.000633</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.583864</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>3.19744</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>3.381163</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>2.622306</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>5.713714</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>2.954681</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>5.914177</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>1.713733</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.046287</v>
       </c>
     </row>
     <row r="35">
@@ -2032,37 +2032,37 @@
         </is>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>3.8e-05</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.000633</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.583864</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>3.19744</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>3.381163</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>2.622306</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>5.713714</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>2.954681</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>5.914177</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>1.713733</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>0.046287</v>
       </c>
     </row>
     <row r="37">
@@ -2572,37 +2572,37 @@
         </is>
       </c>
       <c r="C48" s="3" t="n">
-        <v>3.8e-05</v>
+        <v>0</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.000633</v>
+        <v>0</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.585114</v>
+        <v>0.00125</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>3.470886</v>
+        <v>0.273446</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>3.624687</v>
+        <v>0.243524</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>2.855359</v>
+        <v>0.233053</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>5.892512</v>
+        <v>0.178798</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>3.161319</v>
+        <v>0.206638</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>6.227735</v>
+        <v>0.313558</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>1.964863</v>
+        <v>0.25113</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>0.160391</v>
+        <v>0.114104</v>
       </c>
     </row>
     <row r="49">
@@ -6794,7 +6794,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -10456,7 +10456,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -26502,7 +26502,7 @@
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E265" t="inlineStr">
@@ -27502,7 +27502,7 @@
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E279" t="inlineStr">
@@ -28600,7 +28600,7 @@
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E294" t="inlineStr">
@@ -29352,7 +29352,7 @@
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E304" t="inlineStr">
@@ -30792,7 +30792,7 @@
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E323" t="inlineStr">
@@ -32346,7 +32346,7 @@
       </c>
       <c r="D343" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E343" t="inlineStr">

--- a/output/pdf_financials_xlsx/BRO.xlsx
+++ b/output/pdf_financials_xlsx/BRO.xlsx
@@ -3364,31 +3364,31 @@
         <v>0</v>
       </c>
       <c r="E64" s="3" t="n">
-        <v>0</v>
+        <v>0.050374</v>
       </c>
       <c r="F64" s="3" t="n">
-        <v>0</v>
+        <v>0.136867</v>
       </c>
       <c r="G64" s="3" t="n">
-        <v>0</v>
+        <v>0.12804</v>
       </c>
       <c r="H64" s="3" t="n">
-        <v>0</v>
+        <v>0.124123</v>
       </c>
       <c r="I64" s="3" t="n">
-        <v>0</v>
+        <v>0.206616</v>
       </c>
       <c r="J64" s="3" t="n">
-        <v>0</v>
+        <v>0.476091</v>
       </c>
       <c r="K64" s="3" t="n">
-        <v>0</v>
+        <v>0.139458</v>
       </c>
       <c r="L64" s="3" t="n">
-        <v>0</v>
+        <v>1.443748</v>
       </c>
       <c r="M64" s="3" t="n">
-        <v>0</v>
+        <v>0.224265</v>
       </c>
     </row>
     <row r="65">
@@ -3499,31 +3499,31 @@
         <v>0</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>0</v>
+        <v>0.038677</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>0</v>
+        <v>0.062017</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>0</v>
+        <v>0.142014</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>0</v>
+        <v>0.141859</v>
       </c>
       <c r="I67" s="3" t="n">
-        <v>0</v>
+        <v>0.169567</v>
       </c>
       <c r="J67" s="3" t="n">
-        <v>0</v>
+        <v>0.133922</v>
       </c>
       <c r="K67" s="3" t="n">
-        <v>0</v>
+        <v>0.062158</v>
       </c>
       <c r="L67" s="3" t="n">
-        <v>0</v>
+        <v>0.191554</v>
       </c>
       <c r="M67" s="3" t="n">
-        <v>0</v>
+        <v>0.274551</v>
       </c>
     </row>
     <row r="68">
@@ -5208,7 +5208,7 @@
         </is>
       </c>
       <c r="C104" s="3" t="n">
-        <v>-0.003441</v>
+        <v>0.011033</v>
       </c>
       <c r="D104" s="3" t="n">
         <v>-0.005348</v>
@@ -5298,7 +5298,7 @@
         </is>
       </c>
       <c r="C106" s="3" t="n">
-        <v>-0.001482</v>
+        <v>-0.051405</v>
       </c>
       <c r="D106" s="3" t="n">
         <v>-0.005491</v>
@@ -5502,13 +5502,13 @@
         <v>0</v>
       </c>
       <c r="K110" s="3" t="n">
-        <v>0</v>
+        <v>0.167012</v>
       </c>
       <c r="L110" s="3" t="n">
-        <v>0</v>
+        <v>0.159408</v>
       </c>
       <c r="M110" s="3" t="n">
-        <v>0</v>
+        <v>0.160645</v>
       </c>
     </row>
     <row r="111">
@@ -6363,7 +6363,7 @@
         </is>
       </c>
       <c r="C129" s="3" t="n">
-        <v>0.002</v>
+        <v>0.052</v>
       </c>
       <c r="D129" s="3" t="n">
         <v>0.052</v>
@@ -6408,7 +6408,7 @@
         </is>
       </c>
       <c r="C130" s="3" t="n">
-        <v>0.00383</v>
+        <v>3.8e-05</v>
       </c>
       <c r="D130" s="3" t="n">
         <v>3.8e-05</v>
@@ -6498,7 +6498,7 @@
         </is>
       </c>
       <c r="C132" s="3" t="n">
-        <v>-0.003792</v>
+        <v>0.000595</v>
       </c>
       <c r="D132" s="3" t="n">
         <v>0.000595</v>
@@ -6543,7 +6543,7 @@
         </is>
       </c>
       <c r="C133" s="3" t="n">
-        <v>3.8e-05</v>
+        <v>0.000633</v>
       </c>
       <c r="D133" s="3" t="n">
         <v>0.000633</v>
@@ -6685,7 +6685,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P352"/>
+  <dimension ref="A1:P367"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -11286,7 +11286,11 @@
           <t>Accretion</t>
         </is>
       </c>
-      <c r="D62" t="inlineStr"/>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E62" t="inlineStr">
         <is>
           <t>-</t>
@@ -11586,7 +11590,11 @@
           <t>Deferred tax expense</t>
         </is>
       </c>
-      <c r="D66" t="inlineStr"/>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E66" t="inlineStr">
         <is>
           <t>-</t>
@@ -11874,10 +11882,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F70" s="5" t="n">
+        <v>-0.062295</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
@@ -12138,10 +12144,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F74" s="5" t="n">
+        <v>-0.051405</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
@@ -12398,7 +12402,11 @@
           <t>Proceeds from share issuance</t>
         </is>
       </c>
-      <c r="D78" t="inlineStr"/>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E78" t="inlineStr">
         <is>
           <t>-</t>
@@ -15178,7 +15186,11 @@
           <t>Deferred tax expense (recovery)</t>
         </is>
       </c>
-      <c r="D115" t="inlineStr"/>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E115" t="inlineStr">
         <is>
           <t>-</t>
@@ -15924,7 +15936,11 @@
           <t>Deferred tax recovery</t>
         </is>
       </c>
-      <c r="D125" t="inlineStr"/>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E125" t="inlineStr">
         <is>
           <t>-</t>
@@ -17966,7 +17982,11 @@
           <t>Deferre tax recovery</t>
         </is>
       </c>
-      <c r="D152" t="inlineStr"/>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E152" t="inlineStr">
         <is>
           <t>-</t>
@@ -20160,7 +20180,11 @@
           <t>Proceeds from shares issuance</t>
         </is>
       </c>
-      <c r="D181" t="inlineStr"/>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E181" t="inlineStr">
         <is>
           <t>-</t>
@@ -20550,10 +20574,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F186" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F186" s="5" t="n">
+        <v>0.052</v>
       </c>
       <c r="G186" t="inlineStr">
         <is>
@@ -23796,7 +23818,11 @@
           <t>Proceeds from share issuances</t>
         </is>
       </c>
-      <c r="D229" t="inlineStr"/>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E229" t="inlineStr">
         <is>
           <t>-</t>
@@ -24922,31 +24948,25 @@
           <t>cash_flow</t>
         </is>
       </c>
-      <c r="B244" t="inlineStr">
-        <is>
-          <t>Operating Activities</t>
-        </is>
-      </c>
+      <c r="B244" t="inlineStr"/>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Net loss for the year $</t>
-        </is>
-      </c>
-      <c r="D244" t="inlineStr">
-        <is>
-          <t>NetIncomeFromContinuingOperations</t>
-        </is>
-      </c>
+          <t>For the year ended March</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr"/>
       <c r="E244" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F244" s="5" t="n">
-        <v>-0.027437</v>
-      </c>
-      <c r="G244" s="5" t="n">
-        <v>-0.079038</v>
+        <v>3.1e-05</v>
+      </c>
+      <c r="G244" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H244" t="inlineStr">
         <is>
@@ -25002,12 +25022,12 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>Items not involving cash</t>
+          <t>Cash flows used in operating activities</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Accrued interest and accretion</t>
+          <t>Net loss for the year (109,975)</t>
         </is>
       </c>
       <c r="D245" t="inlineStr"/>
@@ -25017,10 +25037,12 @@
         </is>
       </c>
       <c r="F245" s="5" t="n">
-        <v>0.023127</v>
-      </c>
-      <c r="G245" s="5" t="n">
-        <v>0.033124</v>
+        <v>-0.079038</v>
+      </c>
+      <c r="G245" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H245" t="inlineStr">
         <is>
@@ -25076,29 +25098,27 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>Gain on derecognition of accounts payable</t>
+          <t>Items not affecting cash</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Gain on derecognition of accounts payable and accrued liabilities</t>
-        </is>
-      </c>
-      <c r="D246" t="inlineStr">
-        <is>
-          <t>ChangeInPayablesAndAccruedExpense</t>
-        </is>
-      </c>
+          <t>Accrued interest and accretion 16,974</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr"/>
       <c r="E246" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F246" s="5" t="n">
-        <v>-0.056937</v>
-      </c>
-      <c r="G246" s="5" t="n">
-        <v>-0.016381</v>
+        <v>0.033124</v>
+      </c>
+      <c r="G246" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H246" t="inlineStr">
         <is>
@@ -25154,12 +25174,12 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>Gain on derecognition of accounts payable</t>
+          <t>Items not affecting cash</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Gain on derecognition of accounts payable total</t>
+          <t>Gain on derecognition of payables (32,890)</t>
         </is>
       </c>
       <c r="D247" t="inlineStr"/>
@@ -25169,10 +25189,12 @@
         </is>
       </c>
       <c r="F247" s="5" t="n">
-        <v>-0.061247</v>
-      </c>
-      <c r="G247" s="5" t="n">
-        <v>-0.062295</v>
+        <v>-0.016381</v>
+      </c>
+      <c r="G247" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H247" t="inlineStr">
         <is>
@@ -25228,29 +25250,29 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>Changes in non-cash operating working capital</t>
+          <t>Items not affecting cash</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Amounts receivable</t>
-        </is>
-      </c>
-      <c r="D248" t="inlineStr">
-        <is>
-          <t>ChangeInReceivables</t>
-        </is>
-      </c>
+          <t>Unrealized foreign exchange gain (264)</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr"/>
       <c r="E248" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F248" s="5" t="n">
-        <v>1.3e-05</v>
-      </c>
-      <c r="G248" s="5" t="n">
-        <v>-0.000143</v>
+      <c r="F248" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G248" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H248" t="inlineStr">
         <is>
@@ -25306,29 +25328,27 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>Changes in non-cash operating working capital</t>
+          <t>Changes in non-cash working capital items</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Accounts payable and accrued liabilities</t>
-        </is>
-      </c>
-      <c r="D249" t="inlineStr">
-        <is>
-          <t>ChangeInPayablesAndAccruedExpense</t>
-        </is>
-      </c>
+          <t>Receivables (80)</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr"/>
       <c r="E249" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F249" s="5" t="n">
-        <v>0.053496</v>
-      </c>
-      <c r="G249" s="5" t="n">
-        <v>0.011033</v>
+        <v>-0.000143</v>
+      </c>
+      <c r="G249" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H249" t="inlineStr">
         <is>
@@ -25384,26 +25404,24 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>Changes in non-cash operating working capital</t>
+          <t>Changes in non-cash working capital items</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Prepaid expenses</t>
-        </is>
-      </c>
-      <c r="D250" t="inlineStr">
-        <is>
-          <t>ChangeInPrepaidAssets</t>
-        </is>
-      </c>
+          <t>Prepaid expenses (1,250)</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr"/>
       <c r="E250" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F250" s="5" t="n">
-        <v>0.001946</v>
+      <c r="F250" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G250" t="inlineStr">
         <is>
@@ -25464,25 +25482,31 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>Changes in non-cash operating working capital</t>
+          <t>Changes in non-cash working capital items</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Changes in non-cash operating working capital total</t>
-        </is>
-      </c>
-      <c r="D251" t="inlineStr"/>
+          <t>Accounts payable and accrued liabilities (97,431)</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>ChangeInPayablesAndAccruedExpense</t>
+        </is>
+      </c>
       <c r="E251" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F251" s="5" t="n">
-        <v>-0.005792</v>
-      </c>
-      <c r="G251" s="5" t="n">
-        <v>-0.051405</v>
+        <v>0.011033</v>
+      </c>
+      <c r="G251" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H251" t="inlineStr">
         <is>
@@ -25538,25 +25562,33 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>Financing Activities</t>
+          <t>Cash flows used in investing activities</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Proceeds from loans payable</t>
-        </is>
-      </c>
-      <c r="D252" t="inlineStr"/>
+          <t>Exploration and evaluation asset expenditures (100,073)</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E252" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F252" s="5" t="n">
-        <v>0.002</v>
-      </c>
-      <c r="G252" s="5" t="n">
-        <v>0.052</v>
+      <c r="F252" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G252" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H252" t="inlineStr">
         <is>
@@ -25612,17 +25644,17 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>Financing Activities</t>
+          <t>Cash flows from financing activities</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Financing Activities total</t>
+          <t>Proceeds from share issuances 1,150,000</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>FinancingCashFlow</t>
+          <t>CommonStockIssuance</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
@@ -25630,11 +25662,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F253" s="5" t="n">
-        <v>0.002</v>
-      </c>
-      <c r="G253" s="5" t="n">
-        <v>0.052</v>
+      <c r="F253" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G253" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H253" t="inlineStr">
         <is>
@@ -25690,29 +25726,27 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>Financing Activities</t>
+          <t>Cash flows from financing activities</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Increase (Decrease) in Cash</t>
-        </is>
-      </c>
-      <c r="D254" t="inlineStr">
-        <is>
-          <t>ChangesInCash</t>
-        </is>
-      </c>
+          <t>Proceeds from loans payable 22,400</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr"/>
       <c r="E254" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F254" s="5" t="n">
-        <v>-0.003792</v>
-      </c>
-      <c r="G254" s="5" t="n">
-        <v>0.000595</v>
+        <v>0.052</v>
+      </c>
+      <c r="G254" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H254" t="inlineStr">
         <is>
@@ -25768,29 +25802,29 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>Financing Activities</t>
+          <t>Cash flows from financing activities</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Cash, Beginning of Year</t>
-        </is>
-      </c>
-      <c r="D255" t="inlineStr">
-        <is>
-          <t>BeginningCashPosition</t>
-        </is>
-      </c>
+          <t>Repayment of loans payable (264,180)</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr"/>
       <c r="E255" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F255" s="5" t="n">
-        <v>0.00383</v>
-      </c>
-      <c r="G255" s="5" t="n">
-        <v>3.8e-05</v>
+      <c r="F255" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G255" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H255" t="inlineStr">
         <is>
@@ -25846,17 +25880,17 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>Financing Activities</t>
+          <t>Cash flows from financing activities</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Cash, End of Year $</t>
+          <t>Net change in cash 583,231</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>EndCashPosition</t>
+          <t>ChangesInCash</t>
         </is>
       </c>
       <c r="E256" t="inlineStr">
@@ -25865,10 +25899,12 @@
         </is>
       </c>
       <c r="F256" s="5" t="n">
-        <v>3.8e-05</v>
-      </c>
-      <c r="G256" s="5" t="n">
-        <v>0.000633</v>
+        <v>0.000595</v>
+      </c>
+      <c r="G256" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H256" t="inlineStr">
         <is>
@@ -25924,24 +25960,26 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>Supplemental Cash Flow Information</t>
+          <t>Cash flows from financing activities</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Cash paid for interest $</t>
-        </is>
-      </c>
-      <c r="D257" t="inlineStr"/>
+          <t>Cash, beginning of year 633</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>BeginningCashPosition</t>
+        </is>
+      </c>
       <c r="E257" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F257" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F257" s="5" t="n">
+        <v>3.8e-05</v>
       </c>
       <c r="G257" t="inlineStr">
         <is>
@@ -26002,24 +26040,26 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>Supplemental Cash Flow Information</t>
+          <t>Cash flows from financing activities</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Cash paid for income taxes</t>
-        </is>
-      </c>
-      <c r="D258" t="inlineStr"/>
+          <t>Cash, end of year 583,864</t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>EndCashPosition</t>
+        </is>
+      </c>
       <c r="E258" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F258" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F258" s="5" t="n">
+        <v>0.000633</v>
       </c>
       <c r="G258" t="inlineStr">
         <is>
@@ -26075,148 +26115,174 @@
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Operating Activities</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Advertising and marketing</t>
-        </is>
-      </c>
-      <c r="D259" t="inlineStr"/>
+          <t>Net loss for the year $</t>
+        </is>
+      </c>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E259" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F259" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G259" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F259" s="5" t="n">
+        <v>-0.027437</v>
+      </c>
+      <c r="G259" s="5" t="n">
+        <v>-0.079038</v>
       </c>
       <c r="H259" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I259" s="5" t="n">
-        <v>0.016791</v>
-      </c>
-      <c r="J259" s="5" t="n">
-        <v>0.085852</v>
-      </c>
-      <c r="K259" s="5" t="n">
-        <v>0.183719</v>
-      </c>
-      <c r="L259" s="5" t="n">
-        <v>0.245092</v>
-      </c>
-      <c r="M259" s="5" t="n">
-        <v>0.289724</v>
-      </c>
-      <c r="N259" s="5" t="n">
-        <v>0.352087</v>
-      </c>
-      <c r="O259" s="5" t="n">
-        <v>0.35442</v>
-      </c>
-      <c r="P259" s="5" t="n">
-        <v>0.252623</v>
+      <c r="I259" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J259" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K259" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L259" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M259" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N259" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O259" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P259" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Items not involving cash</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Consulting fees</t>
-        </is>
-      </c>
-      <c r="D260" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
+          <t>Accrued interest and accretion</t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr"/>
       <c r="E260" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F260" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G260" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H260" s="5" t="n">
-        <v>0.04275</v>
-      </c>
-      <c r="I260" s="5" t="n">
-        <v>0.252227</v>
-      </c>
-      <c r="J260" s="5" t="n">
-        <v>0.208974</v>
-      </c>
-      <c r="K260" s="5" t="n">
-        <v>0.123934</v>
-      </c>
-      <c r="L260" s="5" t="n">
-        <v>0.024714</v>
-      </c>
-      <c r="M260" s="5" t="n">
-        <v>0.04813</v>
-      </c>
-      <c r="N260" s="5" t="n">
-        <v>0.003039</v>
-      </c>
-      <c r="O260" s="5" t="n">
-        <v>0.043167</v>
-      </c>
-      <c r="P260" s="5" t="n">
-        <v>0.095161</v>
+      <c r="F260" s="5" t="n">
+        <v>0.023127</v>
+      </c>
+      <c r="G260" s="5" t="n">
+        <v>0.033124</v>
+      </c>
+      <c r="H260" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I260" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J260" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K260" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L260" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M260" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N260" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O260" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P260" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Gain on derecognition of accounts payable</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>Depreciation (Note 5)</t>
+          <t>Gain on derecognition of accounts payable and accrued liabilities</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>Depreciation</t>
+          <t>ChangeInPayablesAndAccruedExpense</t>
         </is>
       </c>
       <c r="E261" t="inlineStr">
@@ -26224,15 +26290,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F261" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G261" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F261" s="5" t="n">
+        <v>-0.056937</v>
+      </c>
+      <c r="G261" s="5" t="n">
+        <v>-0.016381</v>
       </c>
       <c r="H261" t="inlineStr">
         <is>
@@ -26249,8 +26311,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K261" s="5" t="n">
-        <v>0.024939</v>
+      <c r="K261" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L261" t="inlineStr">
         <is>
@@ -26262,30 +26326,36 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N261" s="5" t="n">
-        <v>0.026875</v>
-      </c>
-      <c r="O261" s="5" t="n">
-        <v>0.026875</v>
-      </c>
-      <c r="P261" s="5" t="n">
-        <v>0.026875</v>
+      <c r="N261" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O261" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P261" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Gain on derecognition of accounts payable</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Accretion (Note 7)</t>
+          <t>Gain on derecognition of accounts payable total</t>
         </is>
       </c>
       <c r="D262" t="inlineStr"/>
@@ -26294,15 +26364,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F262" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G262" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F262" s="5" t="n">
+        <v>-0.061247</v>
+      </c>
+      <c r="G262" s="5" t="n">
+        <v>-0.062295</v>
       </c>
       <c r="H262" t="inlineStr">
         <is>
@@ -26334,35 +26400,41 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N262" s="5" t="n">
-        <v>0.167012</v>
-      </c>
-      <c r="O262" s="5" t="n">
-        <v>0.159408</v>
-      </c>
-      <c r="P262" s="5" t="n">
-        <v>0.160645</v>
+      <c r="N262" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O262" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P262" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Changes in non-cash operating working capital</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>Foreign exchange gain</t>
+          <t>Amounts receivable</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>OtherIncomeExpense</t>
+          <t>ChangeInReceivables</t>
         </is>
       </c>
       <c r="E263" t="inlineStr">
@@ -26370,23 +26442,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F263" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G263" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F263" s="5" t="n">
+        <v>1.3e-05</v>
+      </c>
+      <c r="G263" s="5" t="n">
+        <v>-0.000143</v>
       </c>
       <c r="H263" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I263" s="5" t="n">
-        <v>-0.022801</v>
+      <c r="I263" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J263" t="inlineStr">
         <is>
@@ -26408,35 +26478,41 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N263" s="5" t="n">
-        <v>-0.080328</v>
-      </c>
-      <c r="O263" s="5" t="n">
-        <v>-0.031038</v>
-      </c>
-      <c r="P263" s="5" t="n">
-        <v>-0.113146</v>
+      <c r="N263" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O263" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P263" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Changes in non-cash operating working capital</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Insurance</t>
+          <t>Accounts payable and accrued liabilities</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>SellingGeneralAndAdministration</t>
+          <t>ChangeInPayablesAndAccruedExpense</t>
         </is>
       </c>
       <c r="E264" t="inlineStr">
@@ -26444,65 +26520,77 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F264" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G264" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F264" s="5" t="n">
+        <v>0.053496</v>
+      </c>
+      <c r="G264" s="5" t="n">
+        <v>0.011033</v>
       </c>
       <c r="H264" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I264" s="5" t="n">
-        <v>0.006402</v>
-      </c>
-      <c r="J264" s="5" t="n">
-        <v>0.01711</v>
-      </c>
-      <c r="K264" s="5" t="n">
-        <v>0.022622</v>
-      </c>
-      <c r="L264" s="5" t="n">
-        <v>0.026399</v>
-      </c>
-      <c r="M264" s="5" t="n">
-        <v>0.037606</v>
-      </c>
-      <c r="N264" s="5" t="n">
-        <v>0.041964</v>
-      </c>
-      <c r="O264" s="5" t="n">
-        <v>0.045433</v>
-      </c>
-      <c r="P264" s="5" t="n">
-        <v>0.044925</v>
+      <c r="I264" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J264" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K264" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L264" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M264" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N264" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O264" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P264" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Changes in non-cash operating working capital</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>Interest expense (Notes 5 and 7)</t>
+          <t>Prepaid expenses</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>InterestExpenseOperating</t>
+          <t>ChangeInPrepaidAssets</t>
         </is>
       </c>
       <c r="E265" t="inlineStr">
@@ -26510,10 +26598,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F265" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F265" s="5" t="n">
+        <v>0.001946</v>
       </c>
       <c r="G265" t="inlineStr">
         <is>
@@ -26550,117 +26636,123 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N265" s="5" t="n">
-        <v>0.163311</v>
-      </c>
-      <c r="O265" s="5" t="n">
-        <v>0.164469</v>
-      </c>
-      <c r="P265" s="5" t="n">
-        <v>0.152905</v>
+      <c r="N265" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O265" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P265" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Changes in non-cash operating working capital</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Investor relations</t>
-        </is>
-      </c>
-      <c r="D266" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
+          <t>Changes in non-cash operating working capital total</t>
+        </is>
+      </c>
+      <c r="D266" t="inlineStr"/>
       <c r="E266" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F266" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G266" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F266" s="5" t="n">
+        <v>-0.005792</v>
+      </c>
+      <c r="G266" s="5" t="n">
+        <v>-0.051405</v>
       </c>
       <c r="H266" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I266" s="5" t="n">
-        <v>0.006049</v>
-      </c>
-      <c r="J266" s="5" t="n">
-        <v>0.087976</v>
-      </c>
-      <c r="K266" s="5" t="n">
-        <v>0.079136</v>
-      </c>
-      <c r="L266" s="5" t="n">
-        <v>0.01564</v>
-      </c>
-      <c r="M266" s="5" t="n">
-        <v>0.018786</v>
-      </c>
-      <c r="N266" s="5" t="n">
-        <v>0.024229</v>
-      </c>
-      <c r="O266" s="5" t="n">
-        <v>0.029445</v>
-      </c>
-      <c r="P266" s="5" t="n">
-        <v>0.043409</v>
+      <c r="I266" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J266" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K266" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L266" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M266" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N266" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O266" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P266" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Financing Activities</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>Management fees (Note 9)</t>
-        </is>
-      </c>
-      <c r="D267" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
+          <t>Proceeds from loans payable</t>
+        </is>
+      </c>
+      <c r="D267" t="inlineStr"/>
       <c r="E267" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F267" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G267" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F267" s="5" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="G267" s="5" t="n">
+        <v>0.052</v>
       </c>
       <c r="H267" t="inlineStr">
         <is>
@@ -26697,32 +26789,36 @@
           <t>-</t>
         </is>
       </c>
-      <c r="O267" s="5" t="n">
-        <v>0.455812</v>
-      </c>
-      <c r="P267" s="5" t="n">
-        <v>0.463594</v>
+      <c r="O267" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P267" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Financing Activities</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>Office and general</t>
+          <t>Financing Activities total</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>SellingGeneralAndAdministration</t>
+          <t>FinancingCashFlow</t>
         </is>
       </c>
       <c r="E268" t="inlineStr">
@@ -26730,63 +26826,77 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F268" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G268" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H268" s="5" t="n">
-        <v>0.000742</v>
-      </c>
-      <c r="I268" s="5" t="n">
-        <v>0.018998</v>
-      </c>
-      <c r="J268" s="5" t="n">
-        <v>0.043926</v>
-      </c>
-      <c r="K268" s="5" t="n">
-        <v>0.088528</v>
-      </c>
-      <c r="L268" s="5" t="n">
-        <v>0.073281</v>
-      </c>
-      <c r="M268" s="5" t="n">
-        <v>0.08574900000000001</v>
-      </c>
-      <c r="N268" s="5" t="n">
-        <v>0.095164</v>
-      </c>
-      <c r="O268" s="5" t="n">
-        <v>0.253836</v>
-      </c>
-      <c r="P268" s="5" t="n">
-        <v>0.206932</v>
+      <c r="F268" s="5" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="G268" s="5" t="n">
+        <v>0.052</v>
+      </c>
+      <c r="H268" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I268" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J268" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K268" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L268" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M268" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N268" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O268" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P268" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Financing Activities</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>Professional fees (Note 9)</t>
+          <t>Increase (Decrease) in Cash</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>ProfessionalExpenseAndContractServicesExpense</t>
+          <t>ChangesInCash</t>
         </is>
       </c>
       <c r="E269" t="inlineStr">
@@ -26794,15 +26904,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F269" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G269" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F269" s="5" t="n">
+        <v>-0.003792</v>
+      </c>
+      <c r="G269" s="5" t="n">
+        <v>0.000595</v>
       </c>
       <c r="H269" t="inlineStr">
         <is>
@@ -26839,32 +26945,36 @@
           <t>-</t>
         </is>
       </c>
-      <c r="O269" s="5" t="n">
-        <v>0.380485</v>
-      </c>
-      <c r="P269" s="5" t="n">
-        <v>0.261885</v>
+      <c r="O269" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P269" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Financing Activities</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>Rent</t>
+          <t>Cash, Beginning of Year</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>SellingGeneralAndAdministration</t>
+          <t>BeginningCashPosition</t>
         </is>
       </c>
       <c r="E270" t="inlineStr">
@@ -26872,15 +26982,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F270" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G270" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F270" s="5" t="n">
+        <v>0.00383</v>
+      </c>
+      <c r="G270" s="5" t="n">
+        <v>3.8e-05</v>
       </c>
       <c r="H270" t="inlineStr">
         <is>
@@ -26902,53 +27008,63 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L270" s="5" t="n">
-        <v>0.0504</v>
-      </c>
-      <c r="M270" s="5" t="n">
-        <v>0.052176</v>
-      </c>
-      <c r="N270" s="5" t="n">
-        <v>0.075262</v>
-      </c>
-      <c r="O270" s="5" t="n">
-        <v>0.102205</v>
-      </c>
-      <c r="P270" s="5" t="n">
-        <v>0.082853</v>
+      <c r="L270" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M270" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N270" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O270" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P270" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Financing Activities</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>Share-based compensation (Notes 8 and 9)</t>
-        </is>
-      </c>
-      <c r="D271" t="inlineStr"/>
+          <t>Cash, End of Year $</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>EndCashPosition</t>
+        </is>
+      </c>
       <c r="E271" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F271" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G271" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F271" s="5" t="n">
+        <v>3.8e-05</v>
+      </c>
+      <c r="G271" s="5" t="n">
+        <v>0.000633</v>
       </c>
       <c r="H271" t="inlineStr">
         <is>
@@ -26985,34 +27101,34 @@
           <t>-</t>
         </is>
       </c>
-      <c r="O271" s="5" t="n">
-        <v>0.986398</v>
-      </c>
-      <c r="P271" s="5" t="n">
-        <v>0.462714</v>
+      <c r="O271" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P271" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Supplemental Cash Flow Information</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Transfer agent and filing fees</t>
-        </is>
-      </c>
-      <c r="D272" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
+          <t>Cash paid for interest $</t>
+        </is>
+      </c>
+      <c r="D272" t="inlineStr"/>
       <c r="E272" t="inlineStr">
         <is>
           <t>-</t>
@@ -27038,42 +27154,56 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J272" s="5" t="n">
-        <v>0.038033</v>
-      </c>
-      <c r="K272" s="5" t="n">
-        <v>0.047862</v>
-      </c>
-      <c r="L272" s="5" t="n">
-        <v>0.098136</v>
-      </c>
-      <c r="M272" s="5" t="n">
-        <v>0.06861100000000001</v>
-      </c>
-      <c r="N272" s="5" t="n">
-        <v>0.08218200000000001</v>
-      </c>
-      <c r="O272" s="5" t="n">
-        <v>0.098746</v>
-      </c>
-      <c r="P272" s="5" t="n">
-        <v>0.064127</v>
+      <c r="J272" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K272" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L272" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M272" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N272" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O272" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P272" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Supplemental Cash Flow Information</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>Travel and related</t>
+          <t>Cash paid for income taxes</t>
         </is>
       </c>
       <c r="D273" t="inlineStr"/>
@@ -27097,29 +27227,45 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I273" s="5" t="n">
-        <v>0.037437</v>
-      </c>
-      <c r="J273" s="5" t="n">
-        <v>0.047395</v>
-      </c>
-      <c r="K273" s="5" t="n">
-        <v>0.08458599999999999</v>
-      </c>
-      <c r="L273" s="5" t="n">
-        <v>0.013728</v>
-      </c>
-      <c r="M273" s="5" t="n">
-        <v>0.039454</v>
-      </c>
-      <c r="N273" s="5" t="n">
-        <v>0.11726</v>
-      </c>
-      <c r="O273" s="5" t="n">
-        <v>0.082733</v>
-      </c>
-      <c r="P273" s="5" t="n">
-        <v>0.019215</v>
+      <c r="I273" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J273" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K273" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L273" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M273" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N273" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O273" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P273" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="274">
@@ -27135,53 +27281,53 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Expenses total</t>
-        </is>
-      </c>
-      <c r="D274" t="inlineStr">
-        <is>
-          <t>OperatingExpense</t>
-        </is>
-      </c>
+          <t>Advertising and marketing</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr"/>
       <c r="E274" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F274" s="5" t="n">
-        <v>0.095419</v>
+      <c r="F274" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G274" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H274" s="5" t="n">
-        <v>0.142865</v>
+      <c r="H274" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I274" s="5" t="n">
-        <v>2.008448</v>
+        <v>0.016791</v>
       </c>
       <c r="J274" s="5" t="n">
-        <v>1.742677</v>
+        <v>0.085852</v>
       </c>
       <c r="K274" s="5" t="n">
-        <v>2.06189</v>
+        <v>0.183719</v>
       </c>
       <c r="L274" s="5" t="n">
-        <v>2.250631</v>
+        <v>0.245092</v>
       </c>
       <c r="M274" s="5" t="n">
-        <v>2.082576</v>
+        <v>0.289724</v>
       </c>
       <c r="N274" s="5" t="n">
-        <v>2.60497</v>
+        <v>0.352087</v>
       </c>
       <c r="O274" s="5" t="n">
-        <v>3.152394</v>
+        <v>0.35442</v>
       </c>
       <c r="P274" s="5" t="n">
-        <v>2.224717</v>
+        <v>0.252623</v>
       </c>
     </row>
     <row r="275">
@@ -27197,10 +27343,14 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>Gain on write-off of accounts payable</t>
-        </is>
-      </c>
-      <c r="D275" t="inlineStr"/>
+          <t>Consulting fees</t>
+        </is>
+      </c>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E275" t="inlineStr">
         <is>
           <t>-</t>
@@ -27216,48 +27366,32 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H275" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I275" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J275" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K275" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L275" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M275" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N275" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H275" s="5" t="n">
+        <v>0.04275</v>
+      </c>
+      <c r="I275" s="5" t="n">
+        <v>0.252227</v>
+      </c>
+      <c r="J275" s="5" t="n">
+        <v>0.208974</v>
+      </c>
+      <c r="K275" s="5" t="n">
+        <v>0.123934</v>
+      </c>
+      <c r="L275" s="5" t="n">
+        <v>0.024714</v>
+      </c>
+      <c r="M275" s="5" t="n">
+        <v>0.04813</v>
+      </c>
+      <c r="N275" s="5" t="n">
+        <v>0.003039</v>
       </c>
       <c r="O275" s="5" t="n">
-        <v>0.014771</v>
-      </c>
-      <c r="P275" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.043167</v>
+      </c>
+      <c r="P275" s="5" t="n">
+        <v>0.095161</v>
       </c>
     </row>
     <row r="276">
@@ -27273,10 +27407,14 @@
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>Impairment of exploration and evaluation asset (Note 4)</t>
-        </is>
-      </c>
-      <c r="D276" t="inlineStr"/>
+          <t>Depreciation (Note 5)</t>
+        </is>
+      </c>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>Depreciation</t>
+        </is>
+      </c>
       <c r="E276" t="inlineStr">
         <is>
           <t>-</t>
@@ -27307,10 +27445,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K276" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K276" s="5" t="n">
+        <v>0.024939</v>
       </c>
       <c r="L276" t="inlineStr">
         <is>
@@ -27322,16 +27458,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N276" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N276" s="5" t="n">
+        <v>0.026875</v>
       </c>
       <c r="O276" s="5" t="n">
-        <v>-1.518494</v>
+        <v>0.026875</v>
       </c>
       <c r="P276" s="5" t="n">
-        <v>-1.66653</v>
+        <v>0.026875</v>
       </c>
     </row>
     <row r="277">
@@ -27347,7 +27481,7 @@
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>Forgiveness of government loan</t>
+          <t>Accretion (Note 7)</t>
         </is>
       </c>
       <c r="D277" t="inlineStr"/>
@@ -27396,18 +27530,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N277" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N277" s="5" t="n">
+        <v>0.167012</v>
       </c>
       <c r="O277" s="5" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="P277" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.159408</v>
+      </c>
+      <c r="P277" s="5" t="n">
+        <v>0.160645</v>
       </c>
     </row>
     <row r="278">
@@ -27423,10 +27553,14 @@
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>Loss on settlement of debt (Note 7 and 8)</t>
-        </is>
-      </c>
-      <c r="D278" t="inlineStr"/>
+          <t>Foreign exchange gain</t>
+        </is>
+      </c>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>OtherIncomeExpense</t>
+        </is>
+      </c>
       <c r="E278" t="inlineStr">
         <is>
           <t>-</t>
@@ -27447,10 +27581,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I278" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I278" s="5" t="n">
+        <v>-0.022801</v>
       </c>
       <c r="J278" t="inlineStr">
         <is>
@@ -27472,16 +27604,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N278" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N278" s="5" t="n">
+        <v>-0.080328</v>
       </c>
       <c r="O278" s="5" t="n">
-        <v>-0.022539</v>
+        <v>-0.031038</v>
       </c>
       <c r="P278" s="5" t="n">
-        <v>-0.130733</v>
+        <v>-0.113146</v>
       </c>
     </row>
     <row r="279">
@@ -27497,12 +27627,12 @@
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>Interest income</t>
+          <t>Insurance</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>InterestIncomeNonOperating</t>
+          <t>SellingGeneralAndAdministration</t>
         </is>
       </c>
       <c r="E279" t="inlineStr">
@@ -27525,33 +27655,29 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I279" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I279" s="5" t="n">
+        <v>0.006402</v>
       </c>
       <c r="J279" s="5" t="n">
-        <v>0.034357</v>
+        <v>0.01711</v>
       </c>
       <c r="K279" s="5" t="n">
-        <v>0.057159</v>
-      </c>
-      <c r="L279" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.022622</v>
+      </c>
+      <c r="L279" s="5" t="n">
+        <v>0.026399</v>
       </c>
       <c r="M279" s="5" t="n">
-        <v>0.165263</v>
+        <v>0.037606</v>
       </c>
       <c r="N279" s="5" t="n">
-        <v>0.055764</v>
+        <v>0.041964</v>
       </c>
       <c r="O279" s="5" t="n">
-        <v>0.087312</v>
+        <v>0.045433</v>
       </c>
       <c r="P279" s="5" t="n">
-        <v>0.016258</v>
+        <v>0.044925</v>
       </c>
     </row>
     <row r="280">
@@ -27567,12 +27693,12 @@
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>Loss before income tax</t>
+          <t>Interest expense (Notes 5 and 7)</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>PretaxIncome</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E280" t="inlineStr">
@@ -27615,17 +27741,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M280" s="5" t="n">
-        <v>-1.917313</v>
+      <c r="M280" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="N280" s="5" t="n">
-        <v>-3.537643</v>
+        <v>0.163311</v>
       </c>
       <c r="O280" s="5" t="n">
-        <v>-4.571344</v>
+        <v>0.164469</v>
       </c>
       <c r="P280" s="5" t="n">
-        <v>-4.005722</v>
+        <v>0.152905</v>
       </c>
     </row>
     <row r="281">
@@ -27641,10 +27769,14 @@
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>Deferred tax expense</t>
-        </is>
-      </c>
-      <c r="D281" t="inlineStr"/>
+          <t>Investor relations</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E281" t="inlineStr">
         <is>
           <t>-</t>
@@ -27665,43 +27797,29 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I281" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J281" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K281" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L281" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M281" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N281" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I281" s="5" t="n">
+        <v>0.006049</v>
+      </c>
+      <c r="J281" s="5" t="n">
+        <v>0.087976</v>
+      </c>
+      <c r="K281" s="5" t="n">
+        <v>0.079136</v>
+      </c>
+      <c r="L281" s="5" t="n">
+        <v>0.01564</v>
+      </c>
+      <c r="M281" s="5" t="n">
+        <v>0.018786</v>
+      </c>
+      <c r="N281" s="5" t="n">
+        <v>0.024229</v>
       </c>
       <c r="O281" s="5" t="n">
-        <v>-0.054905</v>
-      </c>
-      <c r="P281" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.029445</v>
+      </c>
+      <c r="P281" s="5" t="n">
+        <v>0.043409</v>
       </c>
     </row>
     <row r="282">
@@ -27717,12 +27835,12 @@
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>Loss and comprehensive loss for the year</t>
+          <t>Management fees (Note 9)</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>NetIncome</t>
+          <t>SellingGeneralAndAdministration</t>
         </is>
       </c>
       <c r="E282" t="inlineStr">
@@ -27740,32 +27858,46 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H282" s="5" t="n">
-        <v>-0.109975</v>
-      </c>
-      <c r="I282" s="5" t="n">
-        <v>-1.97038</v>
-      </c>
-      <c r="J282" s="5" t="n">
-        <v>-2.772445</v>
-      </c>
-      <c r="K282" s="5" t="n">
-        <v>-2.004731</v>
-      </c>
-      <c r="L282" s="5" t="n">
-        <v>-2.234694</v>
-      </c>
-      <c r="M282" s="5" t="n">
-        <v>-1.869843</v>
-      </c>
-      <c r="N282" s="5" t="n">
-        <v>-3.486366</v>
+      <c r="H282" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I282" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J282" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K282" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L282" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M282" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N282" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O282" s="5" t="n">
-        <v>-4.626249</v>
+        <v>0.455812</v>
       </c>
       <c r="P282" s="5" t="n">
-        <v>-4.005722</v>
+        <v>0.463594</v>
       </c>
     </row>
     <row r="283">
@@ -27781,12 +27913,12 @@
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>Basic and diluted loss per share</t>
+          <t>Office and general</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>BasicEPS</t>
+          <t>SellingGeneralAndAdministration</t>
         </is>
       </c>
       <c r="E283" t="inlineStr">
@@ -27804,34 +27936,32 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H283" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H283" s="5" t="n">
+        <v>0.000742</v>
       </c>
       <c r="I283" s="5" t="n">
-        <v>-9e-08</v>
+        <v>0.018998</v>
       </c>
       <c r="J283" s="5" t="n">
-        <v>-8e-08</v>
+        <v>0.043926</v>
       </c>
       <c r="K283" s="5" t="n">
-        <v>-5e-08</v>
+        <v>0.088528</v>
       </c>
       <c r="L283" s="5" t="n">
-        <v>-4e-08</v>
+        <v>0.073281</v>
       </c>
       <c r="M283" s="5" t="n">
-        <v>-3e-08</v>
+        <v>0.08574900000000001</v>
       </c>
       <c r="N283" s="5" t="n">
-        <v>-5e-08</v>
+        <v>0.095164</v>
       </c>
       <c r="O283" s="5" t="n">
-        <v>-5.999999999999999e-08</v>
+        <v>0.253836</v>
       </c>
       <c r="P283" s="5" t="n">
-        <v>-3e-08</v>
+        <v>0.206932</v>
       </c>
     </row>
     <row r="284">
@@ -27842,15 +27972,19 @@
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>Weighted average number of common shares</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>Weighted average number of common shares outstanding – basic and diluted</t>
-        </is>
-      </c>
-      <c r="D284" t="inlineStr"/>
+          <t>Professional fees (Note 9)</t>
+        </is>
+      </c>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
+        </is>
+      </c>
       <c r="E284" t="inlineStr">
         <is>
           <t>-</t>
@@ -27896,14 +28030,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N284" s="5" t="n">
-        <v>70.632707</v>
+      <c r="N284" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O284" s="5" t="n">
-        <v>83.537558</v>
+        <v>0.380485</v>
       </c>
       <c r="P284" s="5" t="n">
-        <v>122.747701</v>
+        <v>0.261885</v>
       </c>
     </row>
     <row r="285">
@@ -27919,7 +28055,7 @@
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>Management fees (Note 10)</t>
+          <t>Rent</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
@@ -27962,26 +28098,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L285" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M285" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L285" s="5" t="n">
+        <v>0.0504</v>
+      </c>
+      <c r="M285" s="5" t="n">
+        <v>0.052176</v>
       </c>
       <c r="N285" s="5" t="n">
-        <v>0.53173</v>
+        <v>0.075262</v>
       </c>
       <c r="O285" s="5" t="n">
-        <v>0.455812</v>
-      </c>
-      <c r="P285" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.102205</v>
+      </c>
+      <c r="P285" s="5" t="n">
+        <v>0.082853</v>
       </c>
     </row>
     <row r="286">
@@ -27997,14 +28127,10 @@
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>Professional fees (Note 10)</t>
-        </is>
-      </c>
-      <c r="D286" t="inlineStr">
-        <is>
-          <t>ProfessionalExpenseAndContractServicesExpense</t>
-        </is>
-      </c>
+          <t>Share-based compensation (Notes 8 and 9)</t>
+        </is>
+      </c>
+      <c r="D286" t="inlineStr"/>
       <c r="E286" t="inlineStr">
         <is>
           <t>-</t>
@@ -28050,16 +28176,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N286" s="5" t="n">
-        <v>0.269928</v>
+      <c r="N286" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O286" s="5" t="n">
-        <v>0.380485</v>
-      </c>
-      <c r="P286" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.986398</v>
+      </c>
+      <c r="P286" s="5" t="n">
+        <v>0.462714</v>
       </c>
     </row>
     <row r="287">
@@ -28075,10 +28201,14 @@
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>Share-based compensation (Notes 9 and 10)</t>
-        </is>
-      </c>
-      <c r="D287" t="inlineStr"/>
+          <t>Transfer agent and filing fees</t>
+        </is>
+      </c>
+      <c r="D287" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E287" t="inlineStr">
         <is>
           <t>-</t>
@@ -28104,36 +28234,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J287" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K287" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L287" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M287" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J287" s="5" t="n">
+        <v>0.038033</v>
+      </c>
+      <c r="K287" s="5" t="n">
+        <v>0.047862</v>
+      </c>
+      <c r="L287" s="5" t="n">
+        <v>0.098136</v>
+      </c>
+      <c r="M287" s="5" t="n">
+        <v>0.06861100000000001</v>
       </c>
       <c r="N287" s="5" t="n">
-        <v>0.735255</v>
+        <v>0.08218200000000001</v>
       </c>
       <c r="O287" s="5" t="n">
-        <v>0.986398</v>
-      </c>
-      <c r="P287" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.098746</v>
+      </c>
+      <c r="P287" s="5" t="n">
+        <v>0.064127</v>
       </c>
     </row>
     <row r="288">
@@ -28149,7 +28269,7 @@
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>Forgiveness of government loan (Note 8)</t>
+          <t>Travel and related</t>
         </is>
       </c>
       <c r="D288" t="inlineStr"/>
@@ -28173,43 +28293,29 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I288" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J288" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K288" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L288" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M288" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N288" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I288" s="5" t="n">
+        <v>0.037437</v>
+      </c>
+      <c r="J288" s="5" t="n">
+        <v>0.047395</v>
+      </c>
+      <c r="K288" s="5" t="n">
+        <v>0.08458599999999999</v>
+      </c>
+      <c r="L288" s="5" t="n">
+        <v>0.013728</v>
+      </c>
+      <c r="M288" s="5" t="n">
+        <v>0.039454</v>
+      </c>
+      <c r="N288" s="5" t="n">
+        <v>0.11726</v>
       </c>
       <c r="O288" s="5" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="P288" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.082733</v>
+      </c>
+      <c r="P288" s="5" t="n">
+        <v>0.019215</v>
       </c>
     </row>
     <row r="289">
@@ -28225,65 +28331,53 @@
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>Loss on settlement of debt (Note 7)</t>
-        </is>
-      </c>
-      <c r="D289" t="inlineStr"/>
+          <t>Expenses total</t>
+        </is>
+      </c>
+      <c r="D289" t="inlineStr">
+        <is>
+          <t>OperatingExpense</t>
+        </is>
+      </c>
       <c r="E289" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F289" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F289" s="5" t="n">
+        <v>0.095419</v>
       </c>
       <c r="G289" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H289" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I289" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J289" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K289" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L289" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M289" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H289" s="5" t="n">
+        <v>0.142865</v>
+      </c>
+      <c r="I289" s="5" t="n">
+        <v>2.008448</v>
+      </c>
+      <c r="J289" s="5" t="n">
+        <v>1.742677</v>
+      </c>
+      <c r="K289" s="5" t="n">
+        <v>2.06189</v>
+      </c>
+      <c r="L289" s="5" t="n">
+        <v>2.250631</v>
+      </c>
+      <c r="M289" s="5" t="n">
+        <v>2.082576</v>
       </c>
       <c r="N289" s="5" t="n">
-        <v>-0.988437</v>
+        <v>2.60497</v>
       </c>
       <c r="O289" s="5" t="n">
-        <v>-0.022539</v>
-      </c>
-      <c r="P289" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>3.152394</v>
+      </c>
+      <c r="P289" s="5" t="n">
+        <v>2.224717</v>
       </c>
     </row>
     <row r="290">
@@ -28299,7 +28393,7 @@
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>Deferred tax recovery (expense)</t>
+          <t>Gain on write-off of accounts payable</t>
         </is>
       </c>
       <c r="D290" t="inlineStr"/>
@@ -28348,11 +28442,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N290" s="5" t="n">
-        <v>0.051277</v>
+      <c r="N290" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O290" s="5" t="n">
-        <v>-0.054905</v>
+        <v>0.014771</v>
       </c>
       <c r="P290" t="inlineStr">
         <is>
@@ -28373,14 +28469,10 @@
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>Depreciation (Note 6)</t>
-        </is>
-      </c>
-      <c r="D291" t="inlineStr">
-        <is>
-          <t>Depreciation</t>
-        </is>
-      </c>
+          <t>Impairment of exploration and evaluation asset (Note 4)</t>
+        </is>
+      </c>
+      <c r="D291" t="inlineStr"/>
       <c r="E291" t="inlineStr">
         <is>
           <t>-</t>
@@ -28416,24 +28508,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L291" s="5" t="n">
-        <v>0.038705</v>
-      </c>
-      <c r="M291" s="5" t="n">
-        <v>0.031682</v>
-      </c>
-      <c r="N291" s="5" t="n">
-        <v>0.026875</v>
-      </c>
-      <c r="O291" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P291" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L291" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M291" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N291" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O291" s="5" t="n">
+        <v>-1.518494</v>
+      </c>
+      <c r="P291" s="5" t="n">
+        <v>-1.66653</v>
       </c>
     </row>
     <row r="292">
@@ -28449,7 +28543,7 @@
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>Financing charges</t>
+          <t>Forgiveness of government loan</t>
         </is>
       </c>
       <c r="D292" t="inlineStr"/>
@@ -28493,16 +28587,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M292" s="5" t="n">
-        <v>0.10003</v>
-      </c>
-      <c r="N292" s="5" t="n">
-        <v>0.167012</v>
-      </c>
-      <c r="O292" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M292" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N292" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O292" s="5" t="n">
+        <v>0.02</v>
       </c>
       <c r="P292" t="inlineStr">
         <is>
@@ -28523,14 +28619,10 @@
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>Foreign exchange loss (gain)</t>
-        </is>
-      </c>
-      <c r="D293" t="inlineStr">
-        <is>
-          <t>OtherIncomeExpense</t>
-        </is>
-      </c>
+          <t>Loss on settlement of debt (Note 7 and 8)</t>
+        </is>
+      </c>
+      <c r="D293" t="inlineStr"/>
       <c r="E293" t="inlineStr">
         <is>
           <t>-</t>
@@ -28551,35 +28643,41 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I293" s="5" t="n">
-        <v>-0.022801</v>
-      </c>
-      <c r="J293" s="5" t="n">
-        <v>0.015333</v>
-      </c>
-      <c r="K293" s="5" t="n">
-        <v>-0.010915</v>
+      <c r="I293" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J293" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K293" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L293" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="M293" s="5" t="n">
-        <v>0.078663</v>
-      </c>
-      <c r="N293" s="5" t="n">
-        <v>-0.080328</v>
-      </c>
-      <c r="O293" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P293" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M293" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N293" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O293" s="5" t="n">
+        <v>-0.022539</v>
+      </c>
+      <c r="P293" s="5" t="n">
+        <v>-0.130733</v>
       </c>
     </row>
     <row r="294">
@@ -28595,12 +28693,12 @@
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>Interest expense (Notes 6 and 8)</t>
+          <t>Interest income</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>InterestExpenseOperating</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E294" t="inlineStr">
@@ -28628,34 +28726,28 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J294" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K294" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L294" s="5" t="n">
-        <v>0.006736</v>
+      <c r="J294" s="5" t="n">
+        <v>0.034357</v>
+      </c>
+      <c r="K294" s="5" t="n">
+        <v>0.057159</v>
+      </c>
+      <c r="L294" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M294" s="5" t="n">
-        <v>0.039759</v>
+        <v>0.165263</v>
       </c>
       <c r="N294" s="5" t="n">
-        <v>0.163311</v>
-      </c>
-      <c r="O294" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P294" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.055764</v>
+      </c>
+      <c r="O294" s="5" t="n">
+        <v>0.087312</v>
+      </c>
+      <c r="P294" s="5" t="n">
+        <v>0.016258</v>
       </c>
     </row>
     <row r="295">
@@ -28671,12 +28763,12 @@
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>Management fees (Note 11)</t>
+          <t>Loss before income tax</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>SellingGeneralAndAdministration</t>
+          <t>PretaxIncome</t>
         </is>
       </c>
       <c r="E295" t="inlineStr">
@@ -28714,24 +28806,22 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L295" s="5" t="n">
-        <v>0.516</v>
+      <c r="L295" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M295" s="5" t="n">
-        <v>0.4325</v>
+        <v>-1.917313</v>
       </c>
       <c r="N295" s="5" t="n">
-        <v>0.53173</v>
-      </c>
-      <c r="O295" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P295" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-3.537643</v>
+      </c>
+      <c r="O295" s="5" t="n">
+        <v>-4.571344</v>
+      </c>
+      <c r="P295" s="5" t="n">
+        <v>-4.005722</v>
       </c>
     </row>
     <row r="296">
@@ -28747,14 +28837,10 @@
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>Professional fees (Note 11)</t>
-        </is>
-      </c>
-      <c r="D296" t="inlineStr">
-        <is>
-          <t>ProfessionalExpenseAndContractServicesExpense</t>
-        </is>
-      </c>
+          <t>Deferred tax expense</t>
+        </is>
+      </c>
+      <c r="D296" t="inlineStr"/>
       <c r="E296" t="inlineStr">
         <is>
           <t>-</t>
@@ -28790,19 +28876,23 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L296" s="5" t="n">
-        <v>0.343527</v>
-      </c>
-      <c r="M296" s="5" t="n">
-        <v>0.535731</v>
-      </c>
-      <c r="N296" s="5" t="n">
-        <v>0.269928</v>
-      </c>
-      <c r="O296" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L296" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M296" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N296" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O296" s="5" t="n">
+        <v>-0.054905</v>
       </c>
       <c r="P296" t="inlineStr">
         <is>
@@ -28823,10 +28913,14 @@
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>Share-based compensation (Notes 10 and 11)</t>
-        </is>
-      </c>
-      <c r="D297" t="inlineStr"/>
+          <t>Loss and comprehensive loss for the year</t>
+        </is>
+      </c>
+      <c r="D297" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E297" t="inlineStr">
         <is>
           <t>-</t>
@@ -28842,44 +28936,32 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H297" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I297" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J297" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K297" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H297" s="5" t="n">
+        <v>-0.109975</v>
+      </c>
+      <c r="I297" s="5" t="n">
+        <v>-1.97038</v>
+      </c>
+      <c r="J297" s="5" t="n">
+        <v>-2.772445</v>
+      </c>
+      <c r="K297" s="5" t="n">
+        <v>-2.004731</v>
       </c>
       <c r="L297" s="5" t="n">
-        <v>0.659331</v>
+        <v>-2.234694</v>
       </c>
       <c r="M297" s="5" t="n">
-        <v>0.223975</v>
+        <v>-1.869843</v>
       </c>
       <c r="N297" s="5" t="n">
-        <v>0.735255</v>
-      </c>
-      <c r="O297" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P297" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-3.486366</v>
+      </c>
+      <c r="O297" s="5" t="n">
+        <v>-4.626249</v>
+      </c>
+      <c r="P297" s="5" t="n">
+        <v>-4.005722</v>
       </c>
     </row>
     <row r="298">
@@ -28895,10 +28977,14 @@
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>Loss on settlement of debt (Note 8)</t>
-        </is>
-      </c>
-      <c r="D298" t="inlineStr"/>
+          <t>Basic and diluted loss per share</t>
+        </is>
+      </c>
+      <c r="D298" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
       <c r="E298" t="inlineStr">
         <is>
           <t>-</t>
@@ -28919,43 +29005,29 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I298" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J298" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K298" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L298" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M298" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I298" s="5" t="n">
+        <v>-9e-08</v>
+      </c>
+      <c r="J298" s="5" t="n">
+        <v>-8e-08</v>
+      </c>
+      <c r="K298" s="5" t="n">
+        <v>-5e-08</v>
+      </c>
+      <c r="L298" s="5" t="n">
+        <v>-4e-08</v>
+      </c>
+      <c r="M298" s="5" t="n">
+        <v>-3e-08</v>
       </c>
       <c r="N298" s="5" t="n">
-        <v>-0.988437</v>
-      </c>
-      <c r="O298" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P298" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-5e-08</v>
+      </c>
+      <c r="O298" s="5" t="n">
+        <v>-5.999999999999999e-08</v>
+      </c>
+      <c r="P298" s="5" t="n">
+        <v>-3e-08</v>
       </c>
     </row>
     <row r="299">
@@ -28966,12 +29038,12 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Weighted average number of common shares</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>Deferred tax recovery (Note 16)</t>
+          <t>Weighted average number of common shares outstanding – basic and diluted</t>
         </is>
       </c>
       <c r="D299" t="inlineStr"/>
@@ -29015,21 +29087,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M299" s="5" t="n">
-        <v>0.04747</v>
+      <c r="M299" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="N299" s="5" t="n">
-        <v>0.051277</v>
-      </c>
-      <c r="O299" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P299" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>70.632707</v>
+      </c>
+      <c r="O299" s="5" t="n">
+        <v>83.537558</v>
+      </c>
+      <c r="P299" s="5" t="n">
+        <v>122.747701</v>
       </c>
     </row>
     <row r="300">
@@ -29040,15 +29110,19 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>Weighted average number of common shares outstanding –</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>Weighted average number of common shares outstanding – basic and diluted</t>
-        </is>
-      </c>
-      <c r="D300" t="inlineStr"/>
+          <t>Management fees (Note 10)</t>
+        </is>
+      </c>
+      <c r="D300" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E300" t="inlineStr">
         <is>
           <t>-</t>
@@ -29084,19 +29158,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L300" s="5" t="n">
-        <v>53.672966</v>
-      </c>
-      <c r="M300" s="5" t="n">
-        <v>64.684996</v>
+      <c r="L300" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M300" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="N300" s="5" t="n">
-        <v>70.632707</v>
-      </c>
-      <c r="O300" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.53173</v>
+      </c>
+      <c r="O300" s="5" t="n">
+        <v>0.455812</v>
       </c>
       <c r="P300" t="inlineStr">
         <is>
@@ -29117,12 +29193,12 @@
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>Foreign exchange loss</t>
+          <t>Professional fees (Note 10)</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>OtherIncomeExpense</t>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
         </is>
       </c>
       <c r="E301" t="inlineStr">
@@ -29160,21 +29236,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L301" s="5" t="n">
-        <v>0.080164</v>
-      </c>
-      <c r="M301" s="5" t="n">
-        <v>0.078663</v>
-      </c>
-      <c r="N301" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O301" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L301" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M301" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N301" s="5" t="n">
+        <v>0.269928</v>
+      </c>
+      <c r="O301" s="5" t="n">
+        <v>0.380485</v>
       </c>
       <c r="P301" t="inlineStr">
         <is>
@@ -29195,7 +29271,7 @@
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>Property investigation costs</t>
+          <t>Share-based compensation (Notes 9 and 10)</t>
         </is>
       </c>
       <c r="D302" t="inlineStr"/>
@@ -29234,23 +29310,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L302" s="5" t="n">
-        <v>0.058778</v>
+      <c r="L302" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M302" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="N302" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O302" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N302" s="5" t="n">
+        <v>0.735255</v>
+      </c>
+      <c r="O302" s="5" t="n">
+        <v>0.986398</v>
       </c>
       <c r="P302" t="inlineStr">
         <is>
@@ -29271,7 +29345,7 @@
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>Gain on lease termination (Note 6)</t>
+          <t>Forgiveness of government loan (Note 8)</t>
         </is>
       </c>
       <c r="D303" t="inlineStr"/>
@@ -29310,8 +29384,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L303" s="5" t="n">
-        <v>0.002127</v>
+      <c r="L303" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M303" t="inlineStr">
         <is>
@@ -29323,10 +29399,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="O303" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="O303" s="5" t="n">
+        <v>0.02</v>
       </c>
       <c r="P303" t="inlineStr">
         <is>
@@ -29347,14 +29421,10 @@
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>Interest income (Note 4)</t>
-        </is>
-      </c>
-      <c r="D304" t="inlineStr">
-        <is>
-          <t>InterestIncomeNonOperating</t>
-        </is>
-      </c>
+          <t>Loss on settlement of debt (Note 7)</t>
+        </is>
+      </c>
+      <c r="D304" t="inlineStr"/>
       <c r="E304" t="inlineStr">
         <is>
           <t>-</t>
@@ -29390,21 +29460,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L304" s="5" t="n">
-        <v>0.01381</v>
-      </c>
-      <c r="M304" s="5" t="n">
-        <v>0.165263</v>
-      </c>
-      <c r="N304" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O304" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L304" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M304" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N304" s="5" t="n">
+        <v>-0.988437</v>
+      </c>
+      <c r="O304" s="5" t="n">
+        <v>-0.022539</v>
       </c>
       <c r="P304" t="inlineStr">
         <is>
@@ -29425,14 +29495,10 @@
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>Loss before income taxes</t>
-        </is>
-      </c>
-      <c r="D305" t="inlineStr">
-        <is>
-          <t>PretaxIncome</t>
-        </is>
-      </c>
+          <t>Deferred tax recovery (expense)</t>
+        </is>
+      </c>
+      <c r="D305" t="inlineStr"/>
       <c r="E305" t="inlineStr">
         <is>
           <t>-</t>
@@ -29468,21 +29534,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L305" s="5" t="n">
-        <v>-2.234694</v>
-      </c>
-      <c r="M305" s="5" t="n">
-        <v>-1.917313</v>
-      </c>
-      <c r="N305" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O305" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L305" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M305" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N305" s="5" t="n">
+        <v>0.051277</v>
+      </c>
+      <c r="O305" s="5" t="n">
+        <v>-0.054905</v>
       </c>
       <c r="P305" t="inlineStr">
         <is>
@@ -29503,10 +29569,14 @@
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>Deferred tax recovery (Note 15)</t>
-        </is>
-      </c>
-      <c r="D306" t="inlineStr"/>
+          <t>Depreciation (Note 6)</t>
+        </is>
+      </c>
+      <c r="D306" t="inlineStr">
+        <is>
+          <t>Depreciation</t>
+        </is>
+      </c>
       <c r="E306" t="inlineStr">
         <is>
           <t>-</t>
@@ -29542,18 +29612,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L306" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L306" s="5" t="n">
+        <v>0.038705</v>
       </c>
       <c r="M306" s="5" t="n">
-        <v>0.04747</v>
-      </c>
-      <c r="N306" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.031682</v>
+      </c>
+      <c r="N306" s="5" t="n">
+        <v>0.026875</v>
       </c>
       <c r="O306" t="inlineStr">
         <is>
@@ -29579,14 +29645,10 @@
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>Interest expense on lease liabilities (Note 5)</t>
-        </is>
-      </c>
-      <c r="D307" t="inlineStr">
-        <is>
-          <t>InterestExpenseNonOperating</t>
-        </is>
-      </c>
+          <t>Financing charges</t>
+        </is>
+      </c>
+      <c r="D307" t="inlineStr"/>
       <c r="E307" t="inlineStr">
         <is>
           <t>-</t>
@@ -29617,23 +29679,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K307" s="5" t="n">
-        <v>0.004473</v>
+      <c r="K307" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L307" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="M307" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N307" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M307" s="5" t="n">
+        <v>0.10003</v>
+      </c>
+      <c r="N307" s="5" t="n">
+        <v>0.167012</v>
       </c>
       <c r="O307" t="inlineStr">
         <is>
@@ -29659,12 +29719,12 @@
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>Management fees (Note 8)</t>
+          <t>Foreign exchange loss (gain)</t>
         </is>
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>SellingGeneralAndAdministration</t>
+          <t>OtherIncomeExpense</t>
         </is>
       </c>
       <c r="E308" t="inlineStr">
@@ -29687,31 +29747,25 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I308" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I308" s="5" t="n">
+        <v>-0.022801</v>
       </c>
       <c r="J308" s="5" t="n">
-        <v>0.332966</v>
+        <v>0.015333</v>
       </c>
       <c r="K308" s="5" t="n">
-        <v>0.5220860000000001</v>
+        <v>-0.010915</v>
       </c>
       <c r="L308" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="M308" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N308" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M308" s="5" t="n">
+        <v>0.078663</v>
+      </c>
+      <c r="N308" s="5" t="n">
+        <v>-0.080328</v>
       </c>
       <c r="O308" t="inlineStr">
         <is>
@@ -29737,12 +29791,12 @@
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>Professional fees (Note 8)</t>
+          <t>Interest expense (Notes 6 and 8)</t>
         </is>
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>ProfessionalExpenseAndContractServicesExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E309" t="inlineStr">
@@ -29770,26 +29824,24 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J309" s="5" t="n">
-        <v>0.244701</v>
-      </c>
-      <c r="K309" s="5" t="n">
-        <v>0.243498</v>
-      </c>
-      <c r="L309" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M309" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N309" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J309" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K309" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L309" s="5" t="n">
+        <v>0.006736</v>
+      </c>
+      <c r="M309" s="5" t="n">
+        <v>0.039759</v>
+      </c>
+      <c r="N309" s="5" t="n">
+        <v>0.163311</v>
       </c>
       <c r="O309" t="inlineStr">
         <is>
@@ -29815,10 +29867,14 @@
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>Property investigation costs (Note 8)</t>
-        </is>
-      </c>
-      <c r="D310" t="inlineStr"/>
+          <t>Management fees (Note 11)</t>
+        </is>
+      </c>
+      <c r="D310" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E310" t="inlineStr">
         <is>
           <t>-</t>
@@ -29844,26 +29900,24 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J310" s="5" t="n">
-        <v>0.09353</v>
-      </c>
-      <c r="K310" s="5" t="n">
-        <v>0.047841</v>
-      </c>
-      <c r="L310" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M310" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N310" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J310" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K310" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L310" s="5" t="n">
+        <v>0.516</v>
+      </c>
+      <c r="M310" s="5" t="n">
+        <v>0.4325</v>
+      </c>
+      <c r="N310" s="5" t="n">
+        <v>0.53173</v>
       </c>
       <c r="O310" t="inlineStr">
         <is>
@@ -29889,12 +29943,12 @@
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>Rent (Note 8)</t>
+          <t>Professional fees (Note 11)</t>
         </is>
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t>SellingGeneralAndAdministration</t>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
         </is>
       </c>
       <c r="E311" t="inlineStr">
@@ -29922,26 +29976,24 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J311" s="5" t="n">
-        <v>0.018</v>
-      </c>
-      <c r="K311" s="5" t="n">
-        <v>0.0399</v>
-      </c>
-      <c r="L311" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M311" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N311" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J311" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K311" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L311" s="5" t="n">
+        <v>0.343527</v>
+      </c>
+      <c r="M311" s="5" t="n">
+        <v>0.535731</v>
+      </c>
+      <c r="N311" s="5" t="n">
+        <v>0.269928</v>
       </c>
       <c r="O311" t="inlineStr">
         <is>
@@ -29967,7 +30019,7 @@
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>Share-based compensation (Notes 7 and 8)</t>
+          <t>Share-based compensation (Notes 10 and 11)</t>
         </is>
       </c>
       <c r="D312" t="inlineStr"/>
@@ -29996,26 +30048,24 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J312" s="5" t="n">
-        <v>0.508881</v>
-      </c>
-      <c r="K312" s="5" t="n">
-        <v>0.559681</v>
-      </c>
-      <c r="L312" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M312" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N312" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J312" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K312" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L312" s="5" t="n">
+        <v>0.659331</v>
+      </c>
+      <c r="M312" s="5" t="n">
+        <v>0.223975</v>
+      </c>
+      <c r="N312" s="5" t="n">
+        <v>0.735255</v>
       </c>
       <c r="O312" t="inlineStr">
         <is>
@@ -30041,7 +30091,7 @@
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>Write off of exploration and evaluation assets (Note 4)</t>
+          <t>Loss on settlement of debt (Note 8)</t>
         </is>
       </c>
       <c r="D313" t="inlineStr"/>
@@ -30070,8 +30120,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J313" s="5" t="n">
-        <v>-1.064125</v>
+      <c r="J313" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K313" t="inlineStr">
         <is>
@@ -30088,10 +30140,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N313" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N313" s="5" t="n">
+        <v>-0.988437</v>
       </c>
       <c r="O313" t="inlineStr">
         <is>
@@ -30117,14 +30167,10 @@
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>Weighted average number of common shares outstanding</t>
-        </is>
-      </c>
-      <c r="D314" t="inlineStr">
-        <is>
-          <t>SharesOutstanding</t>
-        </is>
-      </c>
+          <t>Deferred tax recovery (Note 16)</t>
+        </is>
+      </c>
+      <c r="D314" t="inlineStr"/>
       <c r="E314" t="inlineStr">
         <is>
           <t>-</t>
@@ -30140,32 +30186,36 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H314" s="5" t="n">
-        <v>8.679830000000001</v>
-      </c>
-      <c r="I314" s="5" t="n">
-        <v>22.579857</v>
-      </c>
-      <c r="J314" s="5" t="n">
-        <v>33.50558</v>
-      </c>
-      <c r="K314" s="5" t="n">
-        <v>42.45737</v>
+      <c r="H314" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I314" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J314" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K314" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L314" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="M314" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N314" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M314" s="5" t="n">
+        <v>0.04747</v>
+      </c>
+      <c r="N314" s="5" t="n">
+        <v>0.051277</v>
       </c>
       <c r="O314" t="inlineStr">
         <is>
@@ -30186,19 +30236,15 @@
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Weighted average number of common shares outstanding –</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>Management fees (Note 7)</t>
-        </is>
-      </c>
-      <c r="D315" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
+          <t>Weighted average number of common shares outstanding – basic and diluted</t>
+        </is>
+      </c>
+      <c r="D315" t="inlineStr"/>
       <c r="E315" t="inlineStr">
         <is>
           <t>-</t>
@@ -30214,34 +30260,34 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H315" s="5" t="n">
-        <v>0.018</v>
-      </c>
-      <c r="I315" s="5" t="n">
-        <v>0.149535</v>
-      </c>
-      <c r="J315" s="5" t="n">
-        <v>0.332966</v>
+      <c r="H315" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I315" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J315" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K315" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="L315" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M315" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N315" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L315" s="5" t="n">
+        <v>53.672966</v>
+      </c>
+      <c r="M315" s="5" t="n">
+        <v>64.684996</v>
+      </c>
+      <c r="N315" s="5" t="n">
+        <v>70.632707</v>
       </c>
       <c r="O315" t="inlineStr">
         <is>
@@ -30267,12 +30313,12 @@
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>Professional fees (Note 7)</t>
+          <t>Foreign exchange loss</t>
         </is>
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>ProfessionalExpenseAndContractServicesExpense</t>
+          <t>OtherIncomeExpense</t>
         </is>
       </c>
       <c r="E316" t="inlineStr">
@@ -30290,29 +30336,31 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H316" s="5" t="n">
-        <v>0.04984</v>
-      </c>
-      <c r="I316" s="5" t="n">
-        <v>0.337543</v>
-      </c>
-      <c r="J316" s="5" t="n">
-        <v>0.244701</v>
+      <c r="H316" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I316" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J316" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K316" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="L316" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M316" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L316" s="5" t="n">
+        <v>0.080164</v>
+      </c>
+      <c r="M316" s="5" t="n">
+        <v>0.078663</v>
       </c>
       <c r="N316" t="inlineStr">
         <is>
@@ -30343,7 +30391,7 @@
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>Property investigation costs (Note 7)</t>
+          <t>Property investigation costs</t>
         </is>
       </c>
       <c r="D317" t="inlineStr"/>
@@ -30367,21 +30415,23 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I317" s="5" t="n">
-        <v>0.07660500000000001</v>
-      </c>
-      <c r="J317" s="5" t="n">
-        <v>0.09353</v>
+      <c r="I317" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J317" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K317" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="L317" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L317" s="5" t="n">
+        <v>0.058778</v>
       </c>
       <c r="M317" t="inlineStr">
         <is>
@@ -30417,14 +30467,10 @@
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>Rent (Note 7)</t>
-        </is>
-      </c>
-      <c r="D318" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
+          <t>Gain on lease termination (Note 6)</t>
+        </is>
+      </c>
+      <c r="D318" t="inlineStr"/>
       <c r="E318" t="inlineStr">
         <is>
           <t>-</t>
@@ -30445,21 +30491,23 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I318" s="5" t="n">
-        <v>0.008999999999999999</v>
-      </c>
-      <c r="J318" s="5" t="n">
-        <v>0.018</v>
+      <c r="I318" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J318" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K318" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="L318" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L318" s="5" t="n">
+        <v>0.002127</v>
       </c>
       <c r="M318" t="inlineStr">
         <is>
@@ -30495,10 +30543,14 @@
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>Share-based compensation (Note 6 &amp; 7)</t>
-        </is>
-      </c>
-      <c r="D319" t="inlineStr"/>
+          <t>Interest income (Note 4)</t>
+        </is>
+      </c>
+      <c r="D319" t="inlineStr">
+        <is>
+          <t>InterestIncomeNonOperating</t>
+        </is>
+      </c>
       <c r="E319" t="inlineStr">
         <is>
           <t>-</t>
@@ -30519,26 +30571,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I319" s="5" t="n">
-        <v>1.072254</v>
-      </c>
-      <c r="J319" s="5" t="n">
-        <v>0.508881</v>
+      <c r="I319" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J319" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K319" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="L319" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M319" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L319" s="5" t="n">
+        <v>0.01381</v>
+      </c>
+      <c r="M319" s="5" t="n">
+        <v>0.165263</v>
       </c>
       <c r="N319" t="inlineStr">
         <is>
@@ -30569,44 +30621,54 @@
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>Transfer and filing fees</t>
-        </is>
-      </c>
-      <c r="D320" t="inlineStr"/>
+          <t>Loss before income taxes</t>
+        </is>
+      </c>
+      <c r="D320" t="inlineStr">
+        <is>
+          <t>PretaxIncome</t>
+        </is>
+      </c>
       <c r="E320" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F320" s="5" t="n">
-        <v>0.009564</v>
-      </c>
-      <c r="G320" s="5" t="n">
-        <v>0.010147</v>
-      </c>
-      <c r="H320" s="5" t="n">
-        <v>0.014559</v>
-      </c>
-      <c r="I320" s="5" t="n">
-        <v>0.048408</v>
-      </c>
-      <c r="J320" s="5" t="n">
-        <v>0.038033</v>
+      <c r="F320" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G320" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H320" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I320" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J320" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K320" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="L320" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M320" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L320" s="5" t="n">
+        <v>-2.234694</v>
+      </c>
+      <c r="M320" s="5" t="n">
+        <v>-1.917313</v>
       </c>
       <c r="N320" t="inlineStr">
         <is>
@@ -30637,7 +30699,7 @@
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>Gain on derecognition of accounts payable and accrued liabilities</t>
+          <t>Deferred tax recovery (Note 15)</t>
         </is>
       </c>
       <c r="D321" t="inlineStr"/>
@@ -30656,11 +30718,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H321" s="5" t="n">
-        <v>0.03289</v>
-      </c>
-      <c r="I321" s="5" t="n">
-        <v>0.038068</v>
+      <c r="H321" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I321" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J321" t="inlineStr">
         <is>
@@ -30677,10 +30743,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M321" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M321" s="5" t="n">
+        <v>0.04747</v>
       </c>
       <c r="N321" t="inlineStr">
         <is>
@@ -30711,10 +30775,14 @@
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>Write-off of exploration and evaluation assets (Note 4)</t>
-        </is>
-      </c>
-      <c r="D322" t="inlineStr"/>
+          <t>Interest expense on lease liabilities (Note 5)</t>
+        </is>
+      </c>
+      <c r="D322" t="inlineStr">
+        <is>
+          <t>InterestExpenseNonOperating</t>
+        </is>
+      </c>
       <c r="E322" t="inlineStr">
         <is>
           <t>-</t>
@@ -30740,13 +30808,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J322" s="5" t="n">
-        <v>-1.064125</v>
-      </c>
-      <c r="K322" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J322" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K322" s="5" t="n">
+        <v>0.004473</v>
       </c>
       <c r="L322" t="inlineStr">
         <is>
@@ -30787,12 +30855,12 @@
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>Interest expense</t>
+          <t>Management fees (Note 8)</t>
         </is>
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>InterestExpenseOperating</t>
+          <t>SellingGeneralAndAdministration</t>
         </is>
       </c>
       <c r="E323" t="inlineStr">
@@ -30810,23 +30878,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H323" s="5" t="n">
-        <v>0.016974</v>
+      <c r="H323" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I323" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J323" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K323" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J323" s="5" t="n">
+        <v>0.332966</v>
+      </c>
+      <c r="K323" s="5" t="n">
+        <v>0.5220860000000001</v>
       </c>
       <c r="L323" t="inlineStr">
         <is>
@@ -30867,10 +30933,14 @@
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>Share-based compensation (Note 7)</t>
-        </is>
-      </c>
-      <c r="D324" t="inlineStr"/>
+          <t>Professional fees (Note 8)</t>
+        </is>
+      </c>
+      <c r="D324" t="inlineStr">
+        <is>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
+        </is>
+      </c>
       <c r="E324" t="inlineStr">
         <is>
           <t>-</t>
@@ -30891,18 +30961,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I324" s="5" t="n">
-        <v>1.072254</v>
-      </c>
-      <c r="J324" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K324" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I324" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J324" s="5" t="n">
+        <v>0.244701</v>
+      </c>
+      <c r="K324" s="5" t="n">
+        <v>0.243498</v>
       </c>
       <c r="L324" t="inlineStr">
         <is>
@@ -30943,14 +31011,10 @@
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>Basic and diluted loss per share $</t>
-        </is>
-      </c>
-      <c r="D325" t="inlineStr">
-        <is>
-          <t>BasicEPS</t>
-        </is>
-      </c>
+          <t>Property investigation costs (Note 8)</t>
+        </is>
+      </c>
+      <c r="D325" t="inlineStr"/>
       <c r="E325" t="inlineStr">
         <is>
           <t>-</t>
@@ -30966,21 +31030,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H325" s="5" t="n">
-        <v>-1e-08</v>
-      </c>
-      <c r="I325" s="5" t="n">
-        <v>-9e-08</v>
-      </c>
-      <c r="J325" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K325" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H325" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I325" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J325" s="5" t="n">
+        <v>0.09353</v>
+      </c>
+      <c r="K325" s="5" t="n">
+        <v>0.047841</v>
       </c>
       <c r="L325" t="inlineStr">
         <is>
@@ -31014,20 +31078,30 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B326" t="inlineStr"/>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>For the year ended March</t>
-        </is>
-      </c>
-      <c r="D326" t="inlineStr"/>
+          <t>Rent (Note 8)</t>
+        </is>
+      </c>
+      <c r="D326" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E326" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F326" s="5" t="n">
-        <v>3.1e-05</v>
+      <c r="F326" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G326" t="inlineStr">
         <is>
@@ -31044,15 +31118,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J326" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K326" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J326" s="5" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="K326" s="5" t="n">
+        <v>0.0399</v>
       </c>
       <c r="L326" t="inlineStr">
         <is>
@@ -31093,14 +31163,10 @@
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>Consulting fees 42,750</t>
-        </is>
-      </c>
-      <c r="D327" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
+          <t>Share-based compensation (Notes 7 and 8)</t>
+        </is>
+      </c>
+      <c r="D327" t="inlineStr"/>
       <c r="E327" t="inlineStr">
         <is>
           <t>-</t>
@@ -31126,15 +31192,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J327" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K327" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J327" s="5" t="n">
+        <v>0.508881</v>
+      </c>
+      <c r="K327" s="5" t="n">
+        <v>0.559681</v>
       </c>
       <c r="L327" t="inlineStr">
         <is>
@@ -31175,21 +31237,19 @@
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>Interest expenses (Note 5) 16,974</t>
-        </is>
-      </c>
-      <c r="D328" t="inlineStr">
-        <is>
-          <t>InterestExpenseOperating</t>
-        </is>
-      </c>
+          <t>Write off of exploration and evaluation assets (Note 4)</t>
+        </is>
+      </c>
+      <c r="D328" t="inlineStr"/>
       <c r="E328" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F328" s="5" t="n">
-        <v>0.033124</v>
+      <c r="F328" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G328" t="inlineStr">
         <is>
@@ -31206,10 +31266,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J328" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J328" s="5" t="n">
+        <v>-1.064125</v>
       </c>
       <c r="K328" t="inlineStr">
         <is>
@@ -31255,12 +31313,12 @@
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>Management fees (Note 7) 18,000</t>
+          <t>Weighted average number of common shares outstanding</t>
         </is>
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>SellingGeneralAndAdministration</t>
+          <t>SharesOutstanding</t>
         </is>
       </c>
       <c r="E329" t="inlineStr">
@@ -31278,25 +31336,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H329" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I329" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J329" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K329" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H329" s="5" t="n">
+        <v>8.679830000000001</v>
+      </c>
+      <c r="I329" s="5" t="n">
+        <v>22.579857</v>
+      </c>
+      <c r="J329" s="5" t="n">
+        <v>33.50558</v>
+      </c>
+      <c r="K329" s="5" t="n">
+        <v>42.45737</v>
       </c>
       <c r="L329" t="inlineStr">
         <is>
@@ -31337,37 +31387,37 @@
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>Office and rent 742</t>
-        </is>
-      </c>
-      <c r="D330" t="inlineStr"/>
+          <t>Management fees (Note 7)</t>
+        </is>
+      </c>
+      <c r="D330" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E330" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F330" s="5" t="n">
-        <v>0.000969</v>
+      <c r="F330" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G330" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H330" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I330" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J330" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H330" s="5" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="I330" s="5" t="n">
+        <v>0.149535</v>
+      </c>
+      <c r="J330" s="5" t="n">
+        <v>0.332966</v>
       </c>
       <c r="K330" t="inlineStr">
         <is>
@@ -31413,7 +31463,7 @@
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>Professional fees (Note 7) 49,840</t>
+          <t>Professional fees (Note 7)</t>
         </is>
       </c>
       <c r="D331" t="inlineStr">
@@ -31426,28 +31476,24 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F331" s="5" t="n">
-        <v>0.051179</v>
+      <c r="F331" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G331" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H331" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I331" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J331" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H331" s="5" t="n">
+        <v>0.04984</v>
+      </c>
+      <c r="I331" s="5" t="n">
+        <v>0.337543</v>
+      </c>
+      <c r="J331" s="5" t="n">
+        <v>0.244701</v>
       </c>
       <c r="K331" t="inlineStr">
         <is>
@@ -31493,7 +31539,7 @@
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>Transfer and filing fees 14,559</t>
+          <t>Property investigation costs (Note 7)</t>
         </is>
       </c>
       <c r="D332" t="inlineStr"/>
@@ -31502,8 +31548,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F332" s="5" t="n">
-        <v>0.010147</v>
+      <c r="F332" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G332" t="inlineStr">
         <is>
@@ -31515,15 +31563,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I332" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J332" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I332" s="5" t="n">
+        <v>0.07660500000000001</v>
+      </c>
+      <c r="J332" s="5" t="n">
+        <v>0.09353</v>
       </c>
       <c r="K332" t="inlineStr">
         <is>
@@ -31564,22 +31608,28 @@
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>Gain on derecognition of accounts payable</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>Gain on derecognition of accounts payable and accrued liabilities 32,890</t>
-        </is>
-      </c>
-      <c r="D333" t="inlineStr"/>
+          <t>Rent (Note 7)</t>
+        </is>
+      </c>
+      <c r="D333" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E333" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F333" s="5" t="n">
-        <v>0.016381</v>
+      <c r="F333" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G333" t="inlineStr">
         <is>
@@ -31591,15 +31641,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I333" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J333" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I333" s="5" t="n">
+        <v>0.008999999999999999</v>
+      </c>
+      <c r="J333" s="5" t="n">
+        <v>0.018</v>
       </c>
       <c r="K333" t="inlineStr">
         <is>
@@ -31640,26 +31686,24 @@
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>Gain on derecognition of accounts payable</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>Loss and comprehensive loss for the year (109,975)</t>
-        </is>
-      </c>
-      <c r="D334" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Share-based compensation (Note 6 &amp; 7)</t>
+        </is>
+      </c>
+      <c r="D334" t="inlineStr"/>
       <c r="E334" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F334" s="5" t="n">
-        <v>-0.079038</v>
+      <c r="F334" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G334" t="inlineStr">
         <is>
@@ -31671,15 +31715,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I334" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J334" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I334" s="5" t="n">
+        <v>1.072254</v>
+      </c>
+      <c r="J334" s="5" t="n">
+        <v>0.508881</v>
       </c>
       <c r="K334" t="inlineStr">
         <is>
@@ -31720,46 +31760,34 @@
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>Gain on derecognition of accounts payable</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>Basic and diluted loss per share (0.01)</t>
-        </is>
-      </c>
-      <c r="D335" t="inlineStr">
-        <is>
-          <t>BasicEPS</t>
-        </is>
-      </c>
+          <t>Transfer and filing fees</t>
+        </is>
+      </c>
+      <c r="D335" t="inlineStr"/>
       <c r="E335" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F335" s="5" t="n">
-        <v>-2e-08</v>
-      </c>
-      <c r="G335" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H335" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I335" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J335" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.009564</v>
+      </c>
+      <c r="G335" s="5" t="n">
+        <v>0.010147</v>
+      </c>
+      <c r="H335" s="5" t="n">
+        <v>0.014559</v>
+      </c>
+      <c r="I335" s="5" t="n">
+        <v>0.048408</v>
+      </c>
+      <c r="J335" s="5" t="n">
+        <v>0.038033</v>
       </c>
       <c r="K335" t="inlineStr">
         <is>
@@ -31800,41 +31828,35 @@
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>Weighted average number of common</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>Weighted average number of common shares outstanding 8,679,830</t>
-        </is>
-      </c>
-      <c r="D336" t="inlineStr">
-        <is>
-          <t>SharesOutstanding</t>
-        </is>
-      </c>
+          <t>Gain on derecognition of accounts payable and accrued liabilities</t>
+        </is>
+      </c>
+      <c r="D336" t="inlineStr"/>
       <c r="E336" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F336" s="5" t="n">
-        <v>5.091226</v>
+      <c r="F336" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G336" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H336" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I336" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H336" s="5" t="n">
+        <v>0.03289</v>
+      </c>
+      <c r="I336" s="5" t="n">
+        <v>0.038068</v>
       </c>
       <c r="J336" t="inlineStr">
         <is>
@@ -31880,12 +31902,12 @@
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>Issued      Share Capital    Reserves         Deficit        (Deficiency)</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>Balance at March 31, 2015 2,545,583 16,737,805 1,561,278 (18,663,596)</t>
+          <t>Write-off of exploration and evaluation assets (Note 4)</t>
         </is>
       </c>
       <c r="D337" t="inlineStr"/>
@@ -31894,8 +31916,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F337" s="5" t="n">
-        <v>-0.364513</v>
+      <c r="F337" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G337" t="inlineStr">
         <is>
@@ -31912,10 +31936,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J337" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J337" s="5" t="n">
+        <v>-1.064125</v>
       </c>
       <c r="K337" t="inlineStr">
         <is>
@@ -31956,32 +31978,36 @@
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>Issued      Share Capital    Reserves         Deficit        (Deficiency)</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>Net loss for the year - - - (79,038)</t>
-        </is>
-      </c>
-      <c r="D338" t="inlineStr"/>
+          <t>Interest expense</t>
+        </is>
+      </c>
+      <c r="D338" t="inlineStr">
+        <is>
+          <t>InterestExpenseOperating</t>
+        </is>
+      </c>
       <c r="E338" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F338" s="5" t="n">
-        <v>-0.079038</v>
+      <c r="F338" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G338" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H338" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H338" s="5" t="n">
+        <v>0.016974</v>
       </c>
       <c r="I338" t="inlineStr">
         <is>
@@ -32032,12 +32058,12 @@
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>Issued      Share Capital    Reserves         Deficit        (Deficiency)</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>Balance at March 31, 2016 2,545,583 16,737,805 1,561,278 (18,742,634)</t>
+          <t>Share-based compensation (Note 7)</t>
         </is>
       </c>
       <c r="D339" t="inlineStr"/>
@@ -32046,8 +32072,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F339" s="5" t="n">
-        <v>-0.443551</v>
+      <c r="F339" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G339" t="inlineStr">
         <is>
@@ -32059,10 +32087,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I339" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I339" s="5" t="n">
+        <v>1.072254</v>
       </c>
       <c r="J339" t="inlineStr">
         <is>
@@ -32108,37 +32134,39 @@
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>Issued      Share Capital    Reserves         Deficit        (Deficiency)</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>Share issued for cash 11,000,000 1,150,000 - -</t>
-        </is>
-      </c>
-      <c r="D340" t="inlineStr"/>
+          <t>Basic and diluted loss per share $</t>
+        </is>
+      </c>
+      <c r="D340" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
       <c r="E340" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F340" s="5" t="n">
-        <v>1.15</v>
+      <c r="F340" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G340" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H340" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I340" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H340" s="5" t="n">
+        <v>-1e-08</v>
+      </c>
+      <c r="I340" s="5" t="n">
+        <v>-9e-08</v>
       </c>
       <c r="J340" t="inlineStr">
         <is>
@@ -32182,14 +32210,10 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B341" t="inlineStr">
-        <is>
-          <t>Issued      Share Capital    Reserves         Deficit        (Deficiency)</t>
-        </is>
-      </c>
+      <c r="B341" t="inlineStr"/>
       <c r="C341" t="inlineStr">
         <is>
-          <t>Net loss for the year - - - (109,975)</t>
+          <t>For the year ended March</t>
         </is>
       </c>
       <c r="D341" t="inlineStr"/>
@@ -32199,7 +32223,7 @@
         </is>
       </c>
       <c r="F341" s="5" t="n">
-        <v>-0.109975</v>
+        <v>3.1e-05</v>
       </c>
       <c r="G341" t="inlineStr">
         <is>
@@ -32260,22 +32284,28 @@
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>Issued      Share Capital    Reserves         Deficit        (Deficiency)</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>Balance at March 31, 2017 13,545,583 17,887,805 1,561,278 (18,852,609)</t>
-        </is>
-      </c>
-      <c r="D342" t="inlineStr"/>
+          <t>Consulting fees 42,750</t>
+        </is>
+      </c>
+      <c r="D342" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E342" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F342" s="5" t="n">
-        <v>0.5964739999999999</v>
+      <c r="F342" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G342" t="inlineStr">
         <is>
@@ -32341,7 +32371,7 @@
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>Interest expense (Note 6) $</t>
+          <t>Interest expenses (Note 5) 16,974</t>
         </is>
       </c>
       <c r="D343" t="inlineStr">
@@ -32355,10 +32385,12 @@
         </is>
       </c>
       <c r="F343" s="5" t="n">
-        <v>0.023127</v>
-      </c>
-      <c r="G343" s="5" t="n">
         <v>0.033124</v>
+      </c>
+      <c r="G343" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H343" t="inlineStr">
         <is>
@@ -32419,20 +32451,28 @@
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>Office and rent</t>
-        </is>
-      </c>
-      <c r="D344" t="inlineStr"/>
+          <t>Management fees (Note 7) 18,000</t>
+        </is>
+      </c>
+      <c r="D344" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E344" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F344" s="5" t="n">
-        <v>0.00067</v>
-      </c>
-      <c r="G344" s="5" t="n">
-        <v>0.000969</v>
+      <c r="F344" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G344" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H344" t="inlineStr">
         <is>
@@ -32493,24 +32533,22 @@
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>Professional fees</t>
-        </is>
-      </c>
-      <c r="D345" t="inlineStr">
-        <is>
-          <t>ProfessionalExpenseAndContractServicesExpense</t>
-        </is>
-      </c>
+          <t>Office and rent 742</t>
+        </is>
+      </c>
+      <c r="D345" t="inlineStr"/>
       <c r="E345" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F345" s="5" t="n">
-        <v>0.046437</v>
-      </c>
-      <c r="G345" s="5" t="n">
-        <v>0.051179</v>
+        <v>0.000969</v>
+      </c>
+      <c r="G345" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H345" t="inlineStr">
         <is>
@@ -32571,12 +32609,12 @@
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>Loss Before Other Items $</t>
+          <t>Professional fees (Note 7) 49,840</t>
         </is>
       </c>
       <c r="D346" t="inlineStr">
         <is>
-          <t>OperatingIncome</t>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
         </is>
       </c>
       <c r="E346" t="inlineStr">
@@ -32585,10 +32623,12 @@
         </is>
       </c>
       <c r="F346" s="5" t="n">
-        <v>-0.07979799999999999</v>
-      </c>
-      <c r="G346" s="5" t="n">
-        <v>-0.095419</v>
+        <v>0.051179</v>
+      </c>
+      <c r="G346" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H346" t="inlineStr">
         <is>
@@ -32644,26 +32684,22 @@
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>Other Items</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>Foreign exchange loss</t>
-        </is>
-      </c>
-      <c r="D347" t="inlineStr">
-        <is>
-          <t>OtherIncomeExpense</t>
-        </is>
-      </c>
+          <t>Transfer and filing fees 14,559</t>
+        </is>
+      </c>
+      <c r="D347" t="inlineStr"/>
       <c r="E347" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F347" s="5" t="n">
-        <v>-0.004576</v>
+        <v>0.010147</v>
       </c>
       <c r="G347" t="inlineStr">
         <is>
@@ -32729,7 +32765,7 @@
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>Gain on derecognition of accounts payable and accrued liabilities</t>
+          <t>Gain on derecognition of accounts payable and accrued liabilities 32,890</t>
         </is>
       </c>
       <c r="D348" t="inlineStr"/>
@@ -32739,10 +32775,12 @@
         </is>
       </c>
       <c r="F348" s="5" t="n">
-        <v>0.056937</v>
-      </c>
-      <c r="G348" s="5" t="n">
         <v>0.016381</v>
+      </c>
+      <c r="G348" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H348" t="inlineStr">
         <is>
@@ -32803,7 +32841,7 @@
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>Net Loss and Comprehensive Loss $</t>
+          <t>Loss and comprehensive loss for the year (109,975)</t>
         </is>
       </c>
       <c r="D349" t="inlineStr">
@@ -32817,10 +32855,12 @@
         </is>
       </c>
       <c r="F349" s="5" t="n">
-        <v>-0.027437</v>
-      </c>
-      <c r="G349" s="5" t="n">
         <v>-0.079038</v>
+      </c>
+      <c r="G349" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H349" t="inlineStr">
         <is>
@@ -32881,7 +32921,7 @@
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>Basic and Diluted Loss Per Share</t>
+          <t>Basic and diluted loss per share (0.01)</t>
         </is>
       </c>
       <c r="D350" t="inlineStr">
@@ -32895,10 +32935,12 @@
         </is>
       </c>
       <c r="F350" s="5" t="n">
-        <v>-1e-08</v>
-      </c>
-      <c r="G350" s="5" t="n">
         <v>-2e-08</v>
+      </c>
+      <c r="G350" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H350" t="inlineStr">
         <is>
@@ -32954,12 +32996,12 @@
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>Weighted Average Number of</t>
+          <t>Weighted average number of common</t>
         </is>
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>Common Shares Outstanding</t>
+          <t>Weighted average number of common shares outstanding 8,679,830</t>
         </is>
       </c>
       <c r="D351" t="inlineStr">
@@ -32975,8 +33017,10 @@
       <c r="F351" s="5" t="n">
         <v>5.091226</v>
       </c>
-      <c r="G351" s="5" t="n">
-        <v>5.091226</v>
+      <c r="G351" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H351" t="inlineStr">
         <is>
@@ -33032,71 +33076,1223 @@
       </c>
       <c r="B352" t="inlineStr">
         <is>
+          <t>Issued      Share Capital    Reserves         Deficit        (Deficiency)</t>
+        </is>
+      </c>
+      <c r="C352" t="inlineStr">
+        <is>
+          <t>Balance at March 31, 2015 2,545,583 16,737,805 1,561,278 (18,663,596)</t>
+        </is>
+      </c>
+      <c r="D352" t="inlineStr"/>
+      <c r="E352" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F352" s="5" t="n">
+        <v>-0.364513</v>
+      </c>
+      <c r="G352" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H352" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I352" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J352" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K352" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L352" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M352" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N352" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O352" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P352" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B353" t="inlineStr">
+        <is>
+          <t>Issued      Share Capital    Reserves         Deficit        (Deficiency)</t>
+        </is>
+      </c>
+      <c r="C353" t="inlineStr">
+        <is>
+          <t>Net loss for the year - - - (79,038)</t>
+        </is>
+      </c>
+      <c r="D353" t="inlineStr"/>
+      <c r="E353" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F353" s="5" t="n">
+        <v>-0.079038</v>
+      </c>
+      <c r="G353" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H353" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I353" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J353" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K353" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L353" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M353" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N353" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O353" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P353" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B354" t="inlineStr">
+        <is>
+          <t>Issued      Share Capital    Reserves         Deficit        (Deficiency)</t>
+        </is>
+      </c>
+      <c r="C354" t="inlineStr">
+        <is>
+          <t>Balance at March 31, 2016 2,545,583 16,737,805 1,561,278 (18,742,634)</t>
+        </is>
+      </c>
+      <c r="D354" t="inlineStr"/>
+      <c r="E354" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F354" s="5" t="n">
+        <v>-0.443551</v>
+      </c>
+      <c r="G354" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H354" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I354" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J354" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K354" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L354" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M354" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N354" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O354" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P354" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B355" t="inlineStr">
+        <is>
+          <t>Issued      Share Capital    Reserves         Deficit        (Deficiency)</t>
+        </is>
+      </c>
+      <c r="C355" t="inlineStr">
+        <is>
+          <t>Share issued for cash 11,000,000 1,150,000 - -</t>
+        </is>
+      </c>
+      <c r="D355" t="inlineStr"/>
+      <c r="E355" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F355" s="5" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="G355" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H355" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I355" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J355" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K355" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L355" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M355" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N355" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O355" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P355" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B356" t="inlineStr">
+        <is>
+          <t>Issued      Share Capital    Reserves         Deficit        (Deficiency)</t>
+        </is>
+      </c>
+      <c r="C356" t="inlineStr">
+        <is>
+          <t>Net loss for the year - - - (109,975)</t>
+        </is>
+      </c>
+      <c r="D356" t="inlineStr"/>
+      <c r="E356" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F356" s="5" t="n">
+        <v>-0.109975</v>
+      </c>
+      <c r="G356" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H356" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I356" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J356" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K356" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L356" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M356" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N356" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O356" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P356" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B357" t="inlineStr">
+        <is>
+          <t>Issued      Share Capital    Reserves         Deficit        (Deficiency)</t>
+        </is>
+      </c>
+      <c r="C357" t="inlineStr">
+        <is>
+          <t>Balance at March 31, 2017 13,545,583 17,887,805 1,561,278 (18,852,609)</t>
+        </is>
+      </c>
+      <c r="D357" t="inlineStr"/>
+      <c r="E357" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F357" s="5" t="n">
+        <v>0.5964739999999999</v>
+      </c>
+      <c r="G357" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H357" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I357" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J357" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K357" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L357" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M357" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N357" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O357" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P357" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B358" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C358" t="inlineStr">
+        <is>
+          <t>Interest expense (Note 6) $</t>
+        </is>
+      </c>
+      <c r="D358" t="inlineStr">
+        <is>
+          <t>InterestExpenseOperating</t>
+        </is>
+      </c>
+      <c r="E358" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F358" s="5" t="n">
+        <v>0.023127</v>
+      </c>
+      <c r="G358" s="5" t="n">
+        <v>0.033124</v>
+      </c>
+      <c r="H358" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I358" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J358" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K358" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L358" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M358" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N358" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O358" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P358" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B359" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C359" t="inlineStr">
+        <is>
+          <t>Office and rent</t>
+        </is>
+      </c>
+      <c r="D359" t="inlineStr"/>
+      <c r="E359" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F359" s="5" t="n">
+        <v>0.00067</v>
+      </c>
+      <c r="G359" s="5" t="n">
+        <v>0.000969</v>
+      </c>
+      <c r="H359" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I359" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J359" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K359" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L359" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M359" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N359" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O359" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P359" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B360" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C360" t="inlineStr">
+        <is>
+          <t>Professional fees</t>
+        </is>
+      </c>
+      <c r="D360" t="inlineStr">
+        <is>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
+        </is>
+      </c>
+      <c r="E360" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F360" s="5" t="n">
+        <v>0.046437</v>
+      </c>
+      <c r="G360" s="5" t="n">
+        <v>0.051179</v>
+      </c>
+      <c r="H360" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I360" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J360" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K360" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L360" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M360" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N360" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O360" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P360" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B361" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C361" t="inlineStr">
+        <is>
+          <t>Loss Before Other Items $</t>
+        </is>
+      </c>
+      <c r="D361" t="inlineStr">
+        <is>
+          <t>OperatingIncome</t>
+        </is>
+      </c>
+      <c r="E361" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F361" s="5" t="n">
+        <v>-0.07979799999999999</v>
+      </c>
+      <c r="G361" s="5" t="n">
+        <v>-0.095419</v>
+      </c>
+      <c r="H361" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I361" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J361" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K361" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L361" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M361" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N361" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O361" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P361" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B362" t="inlineStr">
+        <is>
+          <t>Other Items</t>
+        </is>
+      </c>
+      <c r="C362" t="inlineStr">
+        <is>
+          <t>Foreign exchange loss</t>
+        </is>
+      </c>
+      <c r="D362" t="inlineStr">
+        <is>
+          <t>OtherIncomeExpense</t>
+        </is>
+      </c>
+      <c r="E362" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F362" s="5" t="n">
+        <v>-0.004576</v>
+      </c>
+      <c r="G362" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H362" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I362" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J362" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K362" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L362" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M362" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N362" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O362" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P362" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B363" t="inlineStr">
+        <is>
+          <t>Gain on derecognition of accounts payable</t>
+        </is>
+      </c>
+      <c r="C363" t="inlineStr">
+        <is>
+          <t>Gain on derecognition of accounts payable and accrued liabilities</t>
+        </is>
+      </c>
+      <c r="D363" t="inlineStr"/>
+      <c r="E363" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F363" s="5" t="n">
+        <v>0.056937</v>
+      </c>
+      <c r="G363" s="5" t="n">
+        <v>0.016381</v>
+      </c>
+      <c r="H363" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I363" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J363" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K363" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L363" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M363" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N363" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O363" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P363" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B364" t="inlineStr">
+        <is>
+          <t>Gain on derecognition of accounts payable</t>
+        </is>
+      </c>
+      <c r="C364" t="inlineStr">
+        <is>
+          <t>Net Loss and Comprehensive Loss $</t>
+        </is>
+      </c>
+      <c r="D364" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E364" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F364" s="5" t="n">
+        <v>-0.027437</v>
+      </c>
+      <c r="G364" s="5" t="n">
+        <v>-0.079038</v>
+      </c>
+      <c r="H364" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I364" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J364" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K364" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L364" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M364" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N364" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O364" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P364" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B365" t="inlineStr">
+        <is>
+          <t>Gain on derecognition of accounts payable</t>
+        </is>
+      </c>
+      <c r="C365" t="inlineStr">
+        <is>
+          <t>Basic and Diluted Loss Per Share</t>
+        </is>
+      </c>
+      <c r="D365" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
+      <c r="E365" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F365" s="5" t="n">
+        <v>-1e-08</v>
+      </c>
+      <c r="G365" s="5" t="n">
+        <v>-2e-08</v>
+      </c>
+      <c r="H365" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I365" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J365" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K365" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L365" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M365" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N365" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O365" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P365" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B366" t="inlineStr">
+        <is>
+          <t>Weighted Average Number of</t>
+        </is>
+      </c>
+      <c r="C366" t="inlineStr">
+        <is>
+          <t>Common Shares Outstanding</t>
+        </is>
+      </c>
+      <c r="D366" t="inlineStr">
+        <is>
+          <t>SharesOutstanding</t>
+        </is>
+      </c>
+      <c r="E366" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F366" s="5" t="n">
+        <v>5.091226</v>
+      </c>
+      <c r="G366" s="5" t="n">
+        <v>5.091226</v>
+      </c>
+      <c r="H366" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I366" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J366" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K366" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L366" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M366" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N366" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O366" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P366" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B367" t="inlineStr">
+        <is>
           <t>Net loss and comprehensive loss for the</t>
         </is>
       </c>
-      <c r="C352" t="inlineStr">
+      <c r="C367" t="inlineStr">
         <is>
           <t>Net loss and comprehensive loss for the year - - -</t>
         </is>
       </c>
-      <c r="D352" t="inlineStr">
+      <c r="D367" t="inlineStr">
         <is>
           <t>NetIncome</t>
         </is>
       </c>
-      <c r="E352" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F352" s="5" t="n">
+      <c r="E367" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F367" s="5" t="n">
         <v>-0.027437</v>
       </c>
-      <c r="G352" s="5" t="n">
+      <c r="G367" s="5" t="n">
         <v>-0.027437</v>
       </c>
-      <c r="H352" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I352" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J352" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K352" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L352" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M352" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N352" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O352" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P352" t="inlineStr">
+      <c r="H367" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I367" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J367" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K367" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L367" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M367" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N367" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O367" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P367" t="inlineStr">
         <is>
           <t>-</t>
         </is>
